--- a/docs/oc-mensuales/suministro-de-combustibles/mar-2026.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/mar-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>10990.3</v>
+        <v>11475.65</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>5495.15</v>
+        <v>5737.83</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5495.15</v>
+        <v>5737.83</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>7693.21</v>
+        <v>8032.96</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>30783.27</v>
+        <v>32142.72</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2307.96</v>
+        <v>2409.89</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3297.09</v>
+        <v>3442.7</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6594.18</v>
+        <v>6885.39</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2307.96</v>
+        <v>2409.89</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4506.02</v>
+        <v>4705.02</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>49456.35</v>
+        <v>51640.44</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>6594.18</v>
+        <v>6885.39</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>6044.67</v>
+        <v>6311.61</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>16485.45</v>
+        <v>17213.48</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>5495.15</v>
+        <v>5737.83</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>10990.3</v>
+        <v>11475.65</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>21980.6</v>
+        <v>22951.31</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2527.77</v>
+        <v>2639.4</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>6594.18</v>
+        <v>6885.39</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2307.96</v>
+        <v>2409.89</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>32970.9</v>
+        <v>34426.96</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>7716.29</v>
+        <v>8057.06</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>9501.120000000001</v>
+        <v>9920.700000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>25662.35</v>
+        <v>26795.65</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>10990.3</v>
+        <v>11475.65</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>14836.91</v>
+        <v>15267.87</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>43961.2</v>
+        <v>45238.12</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3297.09</v>
+        <v>3392.86</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>3297.09</v>
+        <v>3392.86</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3406.99</v>
+        <v>3505.95</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2307.96</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>19782.54</v>
+        <v>20357.15</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2593.9</v>
+        <v>2669.25</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>3320.98</v>
+        <v>3417.44</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>3297.09</v>
+        <v>3392.86</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>10990.3</v>
+        <v>11309.53</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>32970.9</v>
+        <v>33928.59</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>5403.16</v>
+        <v>5560.1</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>63030.98</v>
+        <v>64861.81</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>9359.950000000001</v>
+        <v>9631.82</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>23791.8</v>
+        <v>24482.87</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2857.48</v>
+        <v>2940.48</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3082.67</v>
+        <v>3172.21</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>21980.6</v>
+        <v>22619.06</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>16485.45</v>
+        <v>16964.3</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>7650.46</v>
+        <v>7872.68</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>7651.45</v>
+        <v>7873.7</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2417.87</v>
+        <v>2488.1</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>2307.96</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2307.96</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>48357.32</v>
+        <v>49761.93</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2307.96</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>4875.3</v>
+        <v>5016.91</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>10990.3</v>
+        <v>11309.53</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>8495.66</v>
+        <v>8529.16</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>4839.03</v>
+        <v>4858.11</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>22310.31</v>
+        <v>22398.27</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>18573.61</v>
+        <v>18646.84</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>21980.6</v>
+        <v>22067.26</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>3206.97</v>
+        <v>3219.61</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2307.96</v>
+        <v>2317.06</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>7693.21</v>
+        <v>7723.54</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>5495.15</v>
+        <v>5516.82</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>7693.21</v>
+        <v>7723.54</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>3297.09</v>
+        <v>3310.09</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>32970.9</v>
+        <v>33100.89</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>6594.18</v>
+        <v>6620.18</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>54951.5</v>
+        <v>55168.15</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3297.09</v>
+        <v>3310.09</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>69238.89999999999</v>
+        <v>69511.87</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2307.96</v>
+        <v>2317.06</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>6594.18</v>
+        <v>6620.18</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>8792.24</v>
+        <v>8826.9</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2304.3</v>
+        <v>2313.39</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2307.96</v>
+        <v>2317.06</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2304.3</v>
+        <v>2313.39</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>3791.65</v>
+        <v>3806.6</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>10990.3</v>
+        <v>11033.63</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>16485.45</v>
+        <v>16550.45</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>4945.64</v>
+        <v>4965.13</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2747.58</v>
+        <v>2792.86</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>4396.12</v>
+        <v>4468.57</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>10990.3</v>
+        <v>11171.44</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>5172.72</v>
+        <v>5257.98</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2307.96</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>5495.15</v>
+        <v>5585.72</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>27475.75</v>
+        <v>27928.59</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>5495.15</v>
+        <v>5585.72</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>13188.36</v>
+        <v>13405.72</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>6813.99</v>
+        <v>6926.29</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2417.87</v>
+        <v>2457.72</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>23365.38</v>
+        <v>23750.47</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>32970.9</v>
+        <v>33514.31</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>8792.24</v>
+        <v>8937.15</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>3842.94</v>
+        <v>3906.28</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>10990.3</v>
+        <v>11171.44</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>3297.09</v>
+        <v>3351.43</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>11739.04</v>
+        <v>11932.51</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>43961.2</v>
+        <v>44685.75</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>4396.12</v>
+        <v>4468.57</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>6594.18</v>
+        <v>6702.86</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>4396.12</v>
+        <v>4468.57</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>10990.3</v>
+        <v>11171.44</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>10990.3</v>
+        <v>11171.44</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>8462.530000000001</v>
+        <v>8602.01</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>3846.61</v>
+        <v>3910</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2307.96</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>2307.96</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>16485.45</v>
+        <v>16757.16</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>2373.9</v>
+        <v>2413.03</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>18683.51</v>
+        <v>18991.44</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>4615.93</v>
+        <v>4692</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>26376.72</v>
+        <v>26811.45</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>35168.96</v>
+        <v>35748.6</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>3282.82</v>
+        <v>3290.9</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>37367.02</v>
+        <v>37458.96</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2307.96</v>
+        <v>2313.64</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>2747.58</v>
+        <v>2754.34</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>2747.58</v>
+        <v>2754.34</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>15909.64</v>
+        <v>15948.78</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>3876.88</v>
+        <v>3886.42</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>5495.15</v>
+        <v>5508.67</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>4409.31</v>
+        <v>4420.16</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>10990.3</v>
+        <v>11017.34</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>3297.09</v>
+        <v>3305.2</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>4396.12</v>
+        <v>4406.94</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>2307.96</v>
+        <v>2313.64</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>7693.21</v>
+        <v>7712.14</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>32970.9</v>
+        <v>33052.02</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>23079.63</v>
+        <v>23136.42</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>21980.6</v>
+        <v>22034.68</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>16485.45</v>
+        <v>16526.01</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>2480.48</v>
+        <v>2486.59</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>2307.96</v>
+        <v>2313.64</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>5495.15</v>
+        <v>5508.67</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>6594.18</v>
+        <v>6610.4</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>6594.18</v>
+        <v>6509.29</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>7761.35</v>
+        <v>7661.43</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>5495.15</v>
+        <v>5424.41</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>71436.96000000001</v>
+        <v>70517.27</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>4396.12</v>
+        <v>4339.52</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>22896.09</v>
+        <v>22601.33</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>2307.96</v>
+        <v>2278.25</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2747.58</v>
+        <v>2712.2</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>9891.27</v>
+        <v>9763.93</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>5495.15</v>
+        <v>5424.41</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>10990.3</v>
+        <v>10848.81</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>3297.09</v>
+        <v>3254.64</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>3846.61</v>
+        <v>3797.08</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>5605.05</v>
+        <v>5532.89</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>4396.12</v>
+        <v>4339.52</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>5357.31</v>
+        <v>5288.34</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>10990.3</v>
+        <v>10848.81</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>36817.51</v>
+        <v>36343.52</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>15386.42</v>
+        <v>15188.34</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2472.82</v>
+        <v>2440.98</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>37367.02</v>
+        <v>36885.96</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>2747.58</v>
+        <v>2728.19</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>32970.9</v>
+        <v>32738.23</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>3297.09</v>
+        <v>3273.82</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>4396.12</v>
+        <v>4365.1</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>298936.18</v>
+        <v>296826.57</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>2924.09</v>
+        <v>2903.46</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>2747.58</v>
+        <v>2728.19</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>9290.049999999999</v>
+        <v>9224.49</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>2307.96</v>
+        <v>2291.68</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>7693.21</v>
+        <v>7638.92</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>11701.37</v>
+        <v>11618.8</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>2307.96</v>
+        <v>2291.68</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>2312.08</v>
+        <v>2295.77</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>5495.15</v>
+        <v>5456.37</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>5492.95</v>
+        <v>5454.19</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>2296.97</v>
+        <v>2280.76</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>4396.12</v>
+        <v>4365.1</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>4945.64</v>
+        <v>4910.73</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>29673.81</v>
+        <v>29464.4</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>32970.9</v>
+        <v>32738.23</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>7862.46</v>
+        <v>7806.98</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>37367.02</v>
+        <v>37103.32</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>21980.6</v>
+        <v>21825.48</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>6594.18</v>
+        <v>6547.65</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>3297.09</v>
+        <v>3273.82</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>2307.96</v>
+        <v>2349.81</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>4396.12</v>
+        <v>4475.82</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>2307.96</v>
+        <v>2349.81</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>5495.15</v>
+        <v>5594.78</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>5495.15</v>
+        <v>5594.78</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>21980.6</v>
+        <v>22379.12</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>27475.75</v>
+        <v>27973.91</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>4846.72</v>
+        <v>4934.6</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>2307.96</v>
+        <v>2349.81</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>2615.69</v>
+        <v>2663.12</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>3269.61</v>
+        <v>3328.89</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>2307.96</v>
+        <v>2349.81</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>3269.61</v>
+        <v>3328.89</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>19782.54</v>
+        <v>20141.21</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>13737.88</v>
+        <v>13986.95</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>3297.09</v>
+        <v>3356.87</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>2307.96</v>
+        <v>2349.81</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>5495.15</v>
+        <v>5594.78</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>10990.3</v>
+        <v>11189.56</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>2307.96</v>
+        <v>2349.81</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>21980.6</v>
+        <v>22379.12</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>4396.12</v>
+        <v>4475.82</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>3846.61</v>
+        <v>3916.35</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>27475.75</v>
+        <v>27973.91</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>5400.35</v>
+        <v>5498.26</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>2307.96</v>
+        <v>2349.81</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>6594.18</v>
+        <v>6713.74</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>2874.18</v>
+        <v>2926.29</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>2307.96</v>
+        <v>2349.81</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>6594.18</v>
+        <v>6713.74</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>3297.09</v>
+        <v>3356.87</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>36267.99</v>
+        <v>36925.56</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>8792.24</v>
+        <v>8951.65</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>10990.3</v>
+        <v>11189.56</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>12638.85</v>
+        <v>12868</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>3297.09</v>
+        <v>3356.87</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>16485.45</v>
+        <v>16784.34</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>7693.21</v>
+        <v>7813.72</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>3077.28</v>
+        <v>3125.49</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>27475.75</v>
+        <v>27906.15</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>8792.24</v>
+        <v>8929.969999999999</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>6594.18</v>
+        <v>6697.48</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>10550.69</v>
+        <v>10715.96</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>2747.58</v>
+        <v>2790.61</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>7214.24</v>
+        <v>7327.24</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>2747.58</v>
+        <v>2790.61</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>10990.3</v>
+        <v>11162.46</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>31871.87</v>
+        <v>32371.13</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>5099.5</v>
+        <v>5179.38</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>13203.75</v>
+        <v>13410.58</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>9451.66</v>
+        <v>9599.709999999999</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>13188.36</v>
+        <v>13394.95</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>7143.7</v>
+        <v>7255.6</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>8792.24</v>
+        <v>8929.969999999999</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>21980.6</v>
+        <v>22324.92</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>3661.97</v>
+        <v>3719.33</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>2307.96</v>
+        <v>2344.12</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>3626.8</v>
+        <v>3683.61</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>6484.28</v>
+        <v>6585.85</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>8792.24</v>
+        <v>8929.969999999999</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>4396.12</v>
+        <v>4464.98</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>14003.76</v>
+        <v>14223.12</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>2417.87</v>
+        <v>2417.74</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>2747.58</v>
+        <v>2747.43</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>10007.92</v>
+        <v>10007.41</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>3297.09</v>
+        <v>3296.92</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>9121.950000000001</v>
+        <v>9121.48</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>4396.12</v>
+        <v>4395.89</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>21980.6</v>
+        <v>21979.47</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>49456.35</v>
+        <v>49453.81</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>3297.09</v>
+        <v>3296.92</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>36267.99</v>
+        <v>36266.13</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>7693.21</v>
+        <v>7692.81</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>2747.58</v>
+        <v>2747.43</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>2747.58</v>
+        <v>2747.43</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>6594.18</v>
+        <v>6593.84</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>21980.6</v>
+        <v>21979.47</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>2637.67</v>
+        <v>2637.54</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>13188.36</v>
+        <v>13187.68</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>32970.9</v>
+        <v>32969.21</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>6594.18</v>
+        <v>6593.84</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>4396.12</v>
+        <v>4395.89</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>2967.38</v>
+        <v>2967.23</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>5495.15</v>
+        <v>5494.87</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>21980.6</v>
+        <v>21979.47</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>4945.64</v>
+        <v>4945.38</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>2747.58</v>
+        <v>2747.43</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>4938.05</v>
+        <v>4937.8</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>3461.94</v>
+        <v>3461.77</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>3297.09</v>
+        <v>3296.92</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>5495.15</v>
+        <v>5494.87</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>18683.51</v>
+        <v>18682.55</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>16485.45</v>
+        <v>16411.74</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>2307.96</v>
+        <v>2297.64</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>4396.12</v>
+        <v>4376.46</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>32970.9</v>
+        <v>32823.48</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>4396.12</v>
+        <v>4376.46</v>
       </c>
     </row>
     <row r="281">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>3297.09</v>
+        <v>3282.35</v>
       </c>
     </row>
     <row r="282">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>6594.18</v>
+        <v>6564.7</v>
       </c>
     </row>
     <row r="283">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>5522.63</v>
+        <v>5497.93</v>
       </c>
     </row>
     <row r="284">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>5495.15</v>
+        <v>5470.58</v>
       </c>
     </row>
     <row r="285">
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>5495.15</v>
+        <v>5470.58</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>6594.18</v>
+        <v>6564.7</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>17584.48</v>
+        <v>17505.85</v>
       </c>
     </row>
     <row r="288">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>30772.84</v>
+        <v>30635.24</v>
       </c>
     </row>
     <row r="289">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>5495.15</v>
+        <v>5470.58</v>
       </c>
     </row>
     <row r="290">
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>6731.56</v>
+        <v>6701.46</v>
       </c>
     </row>
     <row r="291">
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>4890.68</v>
+        <v>4868.82</v>
       </c>
     </row>
     <row r="292">
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>5495.15</v>
+        <v>5470.58</v>
       </c>
     </row>
     <row r="293">
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>3297.09</v>
+        <v>3282.35</v>
       </c>
     </row>
     <row r="294">
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>2307.96</v>
+        <v>2297.64</v>
       </c>
     </row>
     <row r="295">
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>3772.58</v>
+        <v>3755.71</v>
       </c>
     </row>
     <row r="296">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>3297.09</v>
+        <v>3282.35</v>
       </c>
     </row>
     <row r="297">
@@ -18564,7 +18564,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>2307.96</v>
+        <v>2309.95</v>
       </c>
     </row>
     <row r="298">
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>5495.15</v>
+        <v>5499.88</v>
       </c>
     </row>
     <row r="299">
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>5495.15</v>
+        <v>5499.88</v>
       </c>
     </row>
     <row r="300">
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>4396.12</v>
+        <v>4399.91</v>
       </c>
     </row>
     <row r="301">
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>2307.96</v>
+        <v>2309.95</v>
       </c>
     </row>
     <row r="302">
@@ -18869,7 +18869,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>3858.16</v>
+        <v>3861.48</v>
       </c>
     </row>
     <row r="303">
@@ -18930,7 +18930,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>2304.3</v>
+        <v>2306.29</v>
       </c>
     </row>
     <row r="304">
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>16485.45</v>
+        <v>16499.65</v>
       </c>
     </row>
     <row r="305">
@@ -19056,7 +19056,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>428621.73</v>
+        <v>428990.99</v>
       </c>
     </row>
     <row r="306">
@@ -19117,7 +19117,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>3297.09</v>
+        <v>3299.93</v>
       </c>
     </row>
     <row r="307">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>4396.12</v>
+        <v>4399.91</v>
       </c>
     </row>
     <row r="308">
@@ -19239,7 +19239,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>9891.27</v>
+        <v>9899.790000000001</v>
       </c>
     </row>
     <row r="309">
@@ -19300,7 +19300,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>8792.24</v>
+        <v>8799.82</v>
       </c>
     </row>
     <row r="310">
@@ -19361,7 +19361,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>4709.23</v>
+        <v>4713.29</v>
       </c>
     </row>
     <row r="311">
@@ -19422,7 +19422,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>2307.96</v>
+        <v>2309.95</v>
       </c>
     </row>
     <row r="312">
@@ -19483,7 +19483,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>2307.96</v>
+        <v>2309.95</v>
       </c>
     </row>
     <row r="313">
@@ -19544,7 +19544,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>6594.18</v>
+        <v>6599.86</v>
       </c>
     </row>
     <row r="314">
@@ -19605,7 +19605,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>2417.87</v>
+        <v>2419.95</v>
       </c>
     </row>
     <row r="315">
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>6008.74</v>
+        <v>6013.91</v>
       </c>
     </row>
     <row r="316">
@@ -19727,7 +19727,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>7325.48</v>
+        <v>7331.79</v>
       </c>
     </row>
     <row r="317">
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>7693.21</v>
+        <v>7699.84</v>
       </c>
     </row>
     <row r="318">
@@ -19849,7 +19849,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>2359.18</v>
+        <v>2361.21</v>
       </c>
     </row>
     <row r="319">
@@ -19910,7 +19910,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>5438.64</v>
+        <v>5443.32</v>
       </c>
     </row>
     <row r="320">
@@ -19971,7 +19971,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>10990.3</v>
+        <v>10999.77</v>
       </c>
     </row>
     <row r="321">
@@ -20032,7 +20032,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>7693.21</v>
+        <v>7699.84</v>
       </c>
     </row>
     <row r="322">
@@ -20093,7 +20093,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>7693.21</v>
+        <v>7699.84</v>
       </c>
     </row>
     <row r="323">
@@ -20154,7 +20154,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>5769.91</v>
+        <v>5774.88</v>
       </c>
     </row>
     <row r="324">
@@ -20215,7 +20215,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>4396.12</v>
+        <v>4399.91</v>
       </c>
     </row>
     <row r="325">
@@ -20276,7 +20276,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>2383.69</v>
+        <v>2385.74</v>
       </c>
     </row>
     <row r="326">
@@ -20337,7 +20337,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>21980.6</v>
+        <v>21999.54</v>
       </c>
     </row>
     <row r="327">
@@ -20398,7 +20398,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>7917.64</v>
+        <v>7924.46</v>
       </c>
     </row>
     <row r="328">
@@ -20459,7 +20459,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>30992.65</v>
+        <v>31019.35</v>
       </c>
     </row>
     <row r="329">
@@ -20520,7 +20520,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>5495.15</v>
+        <v>5499.88</v>
       </c>
     </row>
     <row r="330">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>7143.7</v>
+        <v>7149.85</v>
       </c>
     </row>
     <row r="331">
@@ -20642,7 +20642,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>3297.09</v>
+        <v>3299.93</v>
       </c>
     </row>
     <row r="332">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>2307.96</v>
+        <v>2309.95</v>
       </c>
     </row>
     <row r="333">
@@ -20764,7 +20764,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>13188.36</v>
+        <v>13199.72</v>
       </c>
     </row>
     <row r="334">
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>2307.96</v>
+        <v>2309.95</v>
       </c>
     </row>
     <row r="335">
@@ -20886,7 +20886,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>14287.39</v>
+        <v>14299.7</v>
       </c>
     </row>
     <row r="336">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>2307.96</v>
+        <v>2309.95</v>
       </c>
     </row>
     <row r="337">
@@ -21008,7 +21008,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>2951.07</v>
+        <v>2953.61</v>
       </c>
     </row>
     <row r="338">
@@ -21069,7 +21069,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>3297.09</v>
+        <v>3299.93</v>
       </c>
     </row>
     <row r="339">
@@ -21130,7 +21130,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>4352.99</v>
+        <v>4370.97</v>
       </c>
     </row>
     <row r="340">
@@ -21191,7 +21191,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>32531.29</v>
+        <v>32665.67</v>
       </c>
     </row>
     <row r="341">
@@ -21252,7 +21252,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>2307.96</v>
+        <v>2317.5</v>
       </c>
     </row>
     <row r="342">
@@ -21313,7 +21313,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>3351.79</v>
+        <v>3365.64</v>
       </c>
     </row>
     <row r="343">
@@ -21374,7 +21374,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>7693.21</v>
+        <v>7724.99</v>
       </c>
     </row>
     <row r="344">
@@ -21435,7 +21435,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>3297.09</v>
+        <v>3310.71</v>
       </c>
     </row>
     <row r="345">
@@ -21496,7 +21496,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>32970.9</v>
+        <v>33107.1</v>
       </c>
     </row>
     <row r="346">
@@ -21557,7 +21557,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>2760.77</v>
+        <v>2772.17</v>
       </c>
     </row>
     <row r="347">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>43961.2</v>
+        <v>44142.8</v>
       </c>
     </row>
     <row r="348">
@@ -21679,7 +21679,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>2747.58</v>
+        <v>2758.93</v>
       </c>
     </row>
     <row r="349">
@@ -21740,7 +21740,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>23738.5</v>
+        <v>23836.56</v>
       </c>
     </row>
     <row r="350">
@@ -21801,7 +21801,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>3316.87</v>
+        <v>3330.57</v>
       </c>
     </row>
     <row r="351">
@@ -21862,7 +21862,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>21980.6</v>
+        <v>22071.4</v>
       </c>
     </row>
     <row r="352">
@@ -21923,7 +21923,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>2307.96</v>
+        <v>2317.5</v>
       </c>
     </row>
     <row r="353">
@@ -21984,7 +21984,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>16485.45</v>
+        <v>16553.55</v>
       </c>
     </row>
     <row r="354">
@@ -22045,7 +22045,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>10990.3</v>
+        <v>11035.7</v>
       </c>
     </row>
     <row r="355">
@@ -22106,7 +22106,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>76042.00999999999</v>
+        <v>76356.13</v>
       </c>
     </row>
     <row r="356">
@@ -22167,7 +22167,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>17584.48</v>
+        <v>17657.12</v>
       </c>
     </row>
     <row r="357">
@@ -22228,7 +22228,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>3846.61</v>
+        <v>3862.5</v>
       </c>
     </row>
     <row r="358">
@@ -22289,7 +22289,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>2747.58</v>
+        <v>2758.93</v>
       </c>
     </row>
     <row r="359">
@@ -22350,7 +22350,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>3297.09</v>
+        <v>3310.71</v>
       </c>
     </row>
     <row r="360">
@@ -22411,7 +22411,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>17584.48</v>
+        <v>17657.12</v>
       </c>
     </row>
     <row r="361">
@@ -22472,7 +22472,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>3297.09</v>
+        <v>3310.71</v>
       </c>
     </row>
     <row r="362">
@@ -22533,7 +22533,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>27475.75</v>
+        <v>27589.25</v>
       </c>
     </row>
     <row r="363">
@@ -22594,7 +22594,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>7473.4</v>
+        <v>7504.28</v>
       </c>
     </row>
     <row r="364">
@@ -22655,7 +22655,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>16485.45</v>
+        <v>16553.55</v>
       </c>
     </row>
     <row r="365">
@@ -22716,7 +22716,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>4110.37</v>
+        <v>4127.35</v>
       </c>
     </row>
     <row r="366">
@@ -22777,7 +22777,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>7253.6</v>
+        <v>7283.56</v>
       </c>
     </row>
     <row r="367">
@@ -22838,7 +22838,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>2857.48</v>
+        <v>2869.28</v>
       </c>
     </row>
     <row r="368">
@@ -22899,7 +22899,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>2304.3</v>
+        <v>2313.82</v>
       </c>
     </row>
     <row r="369">
@@ -22960,7 +22960,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>4396.12</v>
+        <v>4414.28</v>
       </c>
     </row>
     <row r="370">
@@ -23021,7 +23021,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>4396.12</v>
+        <v>4383.99</v>
       </c>
     </row>
     <row r="371">
@@ -23082,7 +23082,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>3846.61</v>
+        <v>3835.99</v>
       </c>
     </row>
     <row r="372">
@@ -23143,7 +23143,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>2747.58</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="373">
@@ -23204,7 +23204,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>6594.18</v>
+        <v>6575.99</v>
       </c>
     </row>
     <row r="374">
@@ -23265,7 +23265,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>27288.92</v>
+        <v>27213.64</v>
       </c>
     </row>
     <row r="375">
@@ -23326,7 +23326,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>3472.94</v>
+        <v>3463.36</v>
       </c>
     </row>
     <row r="376">
@@ -23387,7 +23387,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>2527.77</v>
+        <v>2520.8</v>
       </c>
     </row>
     <row r="377">
@@ -23448,7 +23448,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>5045.86</v>
+        <v>5031.94</v>
       </c>
     </row>
     <row r="378">
@@ -23509,7 +23509,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>17584.45</v>
+        <v>17535.94</v>
       </c>
     </row>
     <row r="379">
@@ -23570,7 +23570,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>5483.62</v>
+        <v>5468.49</v>
       </c>
     </row>
     <row r="380">
@@ -23631,7 +23631,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>3297.09</v>
+        <v>3288</v>
       </c>
     </row>
     <row r="381">
@@ -23692,7 +23692,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>18740.96</v>
+        <v>18689.27</v>
       </c>
     </row>
     <row r="382">
@@ -23753,7 +23753,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>4808.26</v>
+        <v>4794.99</v>
       </c>
     </row>
     <row r="383">
@@ -23814,7 +23814,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>10715.54</v>
+        <v>10685.99</v>
       </c>
     </row>
     <row r="384">
@@ -23875,7 +23875,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>4830.35</v>
+        <v>4817.03</v>
       </c>
     </row>
     <row r="385">
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>3297.09</v>
+        <v>3288</v>
       </c>
     </row>
     <row r="386">
@@ -23997,7 +23997,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>3297.09</v>
+        <v>3288</v>
       </c>
     </row>
     <row r="387">
@@ -24058,7 +24058,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>8721.9</v>
+        <v>8697.84</v>
       </c>
     </row>
     <row r="388">
@@ -24119,7 +24119,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>3297.09</v>
+        <v>3288</v>
       </c>
     </row>
     <row r="389">
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>2857.48</v>
+        <v>2849.6</v>
       </c>
     </row>
     <row r="390">
@@ -24241,7 +24241,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>2307.96</v>
+        <v>2301.6</v>
       </c>
     </row>
     <row r="391">
@@ -24302,7 +24302,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>2472.82</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="392">
@@ -24363,7 +24363,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>3297.09</v>
+        <v>3288</v>
       </c>
     </row>
     <row r="393">
@@ -24424,7 +24424,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>2747.58</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="394">
@@ -24485,7 +24485,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>3297.09</v>
+        <v>3288</v>
       </c>
     </row>
     <row r="395">
@@ -24546,7 +24546,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>7253.6</v>
+        <v>7233.59</v>
       </c>
     </row>
     <row r="396">
@@ -24607,7 +24607,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>4066.41</v>
+        <v>4055.19</v>
       </c>
     </row>
     <row r="397">
@@ -24668,7 +24668,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>7877.85</v>
+        <v>7856.12</v>
       </c>
     </row>
     <row r="398">
@@ -24729,7 +24729,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>2307.96</v>
+        <v>2301.6</v>
       </c>
     </row>
     <row r="399">
@@ -24790,7 +24790,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>10990.3</v>
+        <v>10959.99</v>
       </c>
     </row>
     <row r="400">
@@ -24851,7 +24851,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>2417.87</v>
+        <v>2411.2</v>
       </c>
     </row>
     <row r="401">
@@ -24912,7 +24912,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>5495.15</v>
+        <v>5479.99</v>
       </c>
     </row>
     <row r="402">
@@ -24973,7 +24973,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>10990.3</v>
+        <v>10959.99</v>
       </c>
     </row>
     <row r="403">
@@ -25034,7 +25034,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>6594.18</v>
+        <v>6575.99</v>
       </c>
     </row>
     <row r="404">
@@ -25095,7 +25095,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>10990.3</v>
+        <v>10959.99</v>
       </c>
     </row>
     <row r="405">
@@ -25156,7 +25156,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>2307.96</v>
+        <v>2301.6</v>
       </c>
     </row>
     <row r="406">
@@ -25217,7 +25217,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>4396.12</v>
+        <v>4383.99</v>
       </c>
     </row>
     <row r="407">
@@ -25278,7 +25278,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>3406.99</v>
+        <v>3397.6</v>
       </c>
     </row>
     <row r="408">
@@ -25339,7 +25339,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>12226.71</v>
+        <v>12085.56</v>
       </c>
     </row>
     <row r="409">
@@ -25400,7 +25400,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>2307.96</v>
+        <v>2281.32</v>
       </c>
     </row>
     <row r="410">
@@ -25461,7 +25461,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>2305.77</v>
+        <v>2279.15</v>
       </c>
     </row>
     <row r="411">
@@ -25522,7 +25522,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>3846.61</v>
+        <v>3802.2</v>
       </c>
     </row>
     <row r="412">
@@ -25583,7 +25583,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>6044.67</v>
+        <v>5974.88</v>
       </c>
     </row>
     <row r="413">
@@ -25644,7 +25644,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>4558.75</v>
+        <v>4506.13</v>
       </c>
     </row>
     <row r="414">
@@ -25705,7 +25705,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>5714.96</v>
+        <v>5648.98</v>
       </c>
     </row>
     <row r="415">
@@ -25766,7 +25766,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>3881.22</v>
+        <v>3836.42</v>
       </c>
     </row>
     <row r="416">
@@ -25827,7 +25827,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>7693.21</v>
+        <v>7604.4</v>
       </c>
     </row>
     <row r="417">
@@ -25888,7 +25888,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>8792.24</v>
+        <v>8690.74</v>
       </c>
     </row>
     <row r="418">
@@ -25949,7 +25949,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>31157.5</v>
+        <v>30797.81</v>
       </c>
     </row>
     <row r="419">
@@ -26010,7 +26010,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>23739.05</v>
+        <v>23465</v>
       </c>
     </row>
     <row r="420">
@@ -26071,7 +26071,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>5495.15</v>
+        <v>5431.71</v>
       </c>
     </row>
     <row r="421">
@@ -26132,7 +26132,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>8792.24</v>
+        <v>8690.74</v>
       </c>
     </row>
     <row r="422">
@@ -26193,7 +26193,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>3297.09</v>
+        <v>3259.03</v>
       </c>
     </row>
     <row r="423">
@@ -26254,7 +26254,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>5495.15</v>
+        <v>5431.71</v>
       </c>
     </row>
     <row r="424">
@@ -26315,7 +26315,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>2307.96</v>
+        <v>2281.32</v>
       </c>
     </row>
     <row r="425">
@@ -26376,7 +26376,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>2307.96</v>
+        <v>2281.32</v>
       </c>
     </row>
     <row r="426">
@@ -26437,7 +26437,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>5605.05</v>
+        <v>5540.35</v>
       </c>
     </row>
     <row r="427">
@@ -26498,7 +26498,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>3741.27</v>
+        <v>3698.08</v>
       </c>
     </row>
     <row r="428">
@@ -26559,7 +26559,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>4349.96</v>
+        <v>4299.74</v>
       </c>
     </row>
     <row r="429">
@@ -26620,7 +26620,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>12087.66</v>
+        <v>11948.11</v>
       </c>
     </row>
     <row r="430">
@@ -26681,7 +26681,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>10990.3</v>
+        <v>10863.43</v>
       </c>
     </row>
     <row r="431">
@@ -26742,7 +26742,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>9318.690000000001</v>
+        <v>9211.110000000001</v>
       </c>
     </row>
     <row r="432">
@@ -26803,7 +26803,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>4780.78</v>
+        <v>4725.59</v>
       </c>
     </row>
     <row r="433">
@@ -26864,7 +26864,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>14287.39</v>
+        <v>14122.45</v>
       </c>
     </row>
     <row r="434">
@@ -26925,7 +26925,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>4396.12</v>
+        <v>4345.37</v>
       </c>
     </row>
     <row r="435">
@@ -26986,7 +26986,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>2637.67</v>
+        <v>2607.22</v>
       </c>
     </row>
     <row r="436">
@@ -27047,7 +27047,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>21980.6</v>
+        <v>21726.85</v>
       </c>
     </row>
     <row r="437">
@@ -27108,7 +27108,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>5495.15</v>
+        <v>5431.71</v>
       </c>
     </row>
     <row r="438">
@@ -27169,7 +27169,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>2304.3</v>
+        <v>2277.7</v>
       </c>
     </row>
     <row r="439">
@@ -27230,7 +27230,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>2390.39</v>
+        <v>2362.79</v>
       </c>
     </row>
     <row r="440">
@@ -27291,7 +27291,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>2307.96</v>
+        <v>2281.32</v>
       </c>
     </row>
     <row r="441">
@@ -27352,7 +27352,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>2304.3</v>
+        <v>2277.7</v>
       </c>
     </row>
     <row r="442">
@@ -27413,7 +27413,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>10990.3</v>
+        <v>10863.43</v>
       </c>
     </row>
     <row r="443">
@@ -27474,7 +27474,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>2304.3</v>
+        <v>2277.7</v>
       </c>
     </row>
     <row r="444">
@@ -27535,7 +27535,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>3297.09</v>
+        <v>3259.03</v>
       </c>
     </row>
     <row r="445">
@@ -27596,7 +27596,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>2304.3</v>
+        <v>2277.7</v>
       </c>
     </row>
     <row r="446">
@@ -27657,7 +27657,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>2307.96</v>
+        <v>2273.54</v>
       </c>
     </row>
     <row r="447">
@@ -27718,7 +27718,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>21980.6</v>
+        <v>21652.75</v>
       </c>
     </row>
     <row r="448">
@@ -27779,7 +27779,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>13188.36</v>
+        <v>12991.65</v>
       </c>
     </row>
     <row r="449">
@@ -27840,7 +27840,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>3297.09</v>
+        <v>3247.91</v>
       </c>
     </row>
     <row r="450">
@@ -27901,7 +27901,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>2307.96</v>
+        <v>2273.54</v>
       </c>
     </row>
     <row r="451">
@@ -27962,7 +27962,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>4396.12</v>
+        <v>4330.55</v>
       </c>
     </row>
     <row r="452">
@@ -28023,7 +28023,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>2417.87</v>
+        <v>2381.8</v>
       </c>
     </row>
     <row r="453">
@@ -28084,7 +28084,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>5495.15</v>
+        <v>5413.19</v>
       </c>
     </row>
     <row r="454">
@@ -28145,7 +28145,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>27898.48</v>
+        <v>27482.37</v>
       </c>
     </row>
     <row r="455">
@@ -28206,7 +28206,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>3297.09</v>
+        <v>3247.91</v>
       </c>
     </row>
     <row r="456">
@@ -28267,7 +28267,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>14287.39</v>
+        <v>14074.29</v>
       </c>
     </row>
     <row r="457">
@@ -28328,7 +28328,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>21980.6</v>
+        <v>21652.75</v>
       </c>
     </row>
     <row r="458">
@@ -28389,7 +28389,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>4945.64</v>
+        <v>4871.87</v>
       </c>
     </row>
     <row r="459">
@@ -28450,7 +28450,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>3313.58</v>
+        <v>3264.15</v>
       </c>
     </row>
     <row r="460">
@@ -28511,7 +28511,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>76602.39999999999</v>
+        <v>75459.85000000001</v>
       </c>
     </row>
     <row r="461">
@@ -28572,7 +28572,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>7693.21</v>
+        <v>7578.46</v>
       </c>
     </row>
     <row r="462">
@@ -28633,7 +28633,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>2307.96</v>
+        <v>2273.54</v>
       </c>
     </row>
     <row r="463">
@@ -28694,7 +28694,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>4651.1</v>
+        <v>4581.72</v>
       </c>
     </row>
     <row r="464">
@@ -28755,7 +28755,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>10990.3</v>
+        <v>10826.38</v>
       </c>
     </row>
     <row r="465">
@@ -28816,7 +28816,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>3297.09</v>
+        <v>3247.91</v>
       </c>
     </row>
     <row r="466">
@@ -28877,7 +28877,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>21980.6</v>
+        <v>21652.75</v>
       </c>
     </row>
     <row r="467">
@@ -28938,7 +28938,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>4396.12</v>
+        <v>4330.55</v>
       </c>
     </row>
     <row r="468">
@@ -28999,7 +28999,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>2307.96</v>
+        <v>2273.54</v>
       </c>
     </row>
     <row r="469">
@@ -29060,7 +29060,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>17804.29</v>
+        <v>17538.73</v>
       </c>
     </row>
     <row r="470">
@@ -29121,7 +29121,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>2307.96</v>
+        <v>2273.54</v>
       </c>
     </row>
     <row r="471">
@@ -29182,7 +29182,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>2527.77</v>
+        <v>2490.07</v>
       </c>
     </row>
     <row r="472">
@@ -29243,7 +29243,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>5385.25</v>
+        <v>5304.92</v>
       </c>
     </row>
     <row r="473">
@@ -29304,7 +29304,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>2307.96</v>
+        <v>2273.54</v>
       </c>
     </row>
     <row r="474">
@@ -29365,7 +29365,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>8792.24</v>
+        <v>8661.1</v>
       </c>
     </row>
     <row r="475">
@@ -29426,7 +29426,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>2543.16</v>
+        <v>2505.22</v>
       </c>
     </row>
     <row r="476">
@@ -29487,7 +29487,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>2747.58</v>
+        <v>2706.59</v>
       </c>
     </row>
     <row r="477">
@@ -29548,7 +29548,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>2307.96</v>
+        <v>2273.54</v>
       </c>
     </row>
     <row r="478">
@@ -29609,7 +29609,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>3231.62</v>
+        <v>3183.42</v>
       </c>
     </row>
     <row r="479">
@@ -29670,7 +29670,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>4396.11</v>
+        <v>4330.54</v>
       </c>
     </row>
     <row r="480">
@@ -29731,7 +29731,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>3297.09</v>
+        <v>3247.91</v>
       </c>
     </row>
     <row r="481">
@@ -29792,7 +29792,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>7693.21</v>
+        <v>7578.46</v>
       </c>
     </row>
     <row r="482">
@@ -29853,7 +29853,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>5495.15</v>
+        <v>5413.19</v>
       </c>
     </row>
     <row r="483">
@@ -29914,7 +29914,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>2527.77</v>
+        <v>2490.07</v>
       </c>
     </row>
     <row r="484">
@@ -29975,7 +29975,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>2307.96</v>
+        <v>2273.54</v>
       </c>
     </row>
     <row r="485">
@@ -30036,7 +30036,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>16485.45</v>
+        <v>16390.76</v>
       </c>
     </row>
     <row r="486">
@@ -30097,7 +30097,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>8792.24</v>
+        <v>8741.74</v>
       </c>
     </row>
     <row r="487">
@@ -30158,7 +30158,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>6594.18</v>
+        <v>6556.3</v>
       </c>
     </row>
     <row r="488">
@@ -30219,7 +30219,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>4396.12</v>
+        <v>4370.87</v>
       </c>
     </row>
     <row r="489">
@@ -30280,7 +30280,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>6813.99</v>
+        <v>6774.85</v>
       </c>
     </row>
     <row r="490">
@@ -30341,7 +30341,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>3297.09</v>
+        <v>3278.15</v>
       </c>
     </row>
     <row r="491">
@@ -30402,7 +30402,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>7693.21</v>
+        <v>7649.02</v>
       </c>
     </row>
     <row r="492">
@@ -30463,7 +30463,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>4396.12</v>
+        <v>4370.87</v>
       </c>
     </row>
     <row r="493">
@@ -30524,7 +30524,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>10770.49</v>
+        <v>10708.63</v>
       </c>
     </row>
     <row r="494">
@@ -30585,7 +30585,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>6594.18</v>
+        <v>6556.3</v>
       </c>
     </row>
     <row r="495">
@@ -30646,7 +30646,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>3297.09</v>
+        <v>3278.15</v>
       </c>
     </row>
     <row r="496">
@@ -30707,7 +30707,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>4945.64</v>
+        <v>4917.23</v>
       </c>
     </row>
     <row r="497">
@@ -30768,7 +30768,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>10346.27</v>
+        <v>10286.84</v>
       </c>
     </row>
     <row r="498">
@@ -30829,7 +30829,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>4396.12</v>
+        <v>4370.87</v>
       </c>
     </row>
     <row r="499">
@@ -30890,7 +30890,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>10990.3</v>
+        <v>10927.17</v>
       </c>
     </row>
     <row r="500">
@@ -30951,7 +30951,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>3297.09</v>
+        <v>3278.15</v>
       </c>
     </row>
     <row r="501">
@@ -31012,7 +31012,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>2307.96</v>
+        <v>2294.71</v>
       </c>
     </row>
     <row r="502">
@@ -31073,7 +31073,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>10990.3</v>
+        <v>10927.17</v>
       </c>
     </row>
     <row r="503">
@@ -31134,7 +31134,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>12089.33</v>
+        <v>12019.89</v>
       </c>
     </row>
     <row r="504">
@@ -31195,7 +31195,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>9775.33</v>
+        <v>9719.18</v>
       </c>
     </row>
     <row r="505">
@@ -31256,7 +31256,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>37367.02</v>
+        <v>37152.38</v>
       </c>
     </row>
     <row r="506">
@@ -31317,7 +31317,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>4840.13</v>
+        <v>4812.33</v>
       </c>
     </row>
     <row r="507">
@@ -31378,7 +31378,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>2810.57</v>
+        <v>2794.42</v>
       </c>
     </row>
     <row r="508">
@@ -31439,7 +31439,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>2307.96</v>
+        <v>2294.71</v>
       </c>
     </row>
     <row r="509">
@@ -31500,7 +31500,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>2304.34</v>
+        <v>2291.1</v>
       </c>
     </row>
     <row r="510">
@@ -31561,7 +31561,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>6594.18</v>
+        <v>6556.3</v>
       </c>
     </row>
     <row r="511">
@@ -31622,7 +31622,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>5495.15</v>
+        <v>5463.59</v>
       </c>
     </row>
     <row r="512">
@@ -31683,7 +31683,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>21980.6</v>
+        <v>21854.34</v>
       </c>
     </row>
     <row r="513">
@@ -31744,7 +31744,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>75833.08</v>
+        <v>75397.48</v>
       </c>
     </row>
     <row r="514">
@@ -31805,7 +31805,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>5130.18</v>
+        <v>5100.71</v>
       </c>
     </row>
     <row r="515">
@@ -31866,7 +31866,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>3846.61</v>
+        <v>3824.51</v>
       </c>
     </row>
     <row r="516">
@@ -31927,7 +31927,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>5495.15</v>
+        <v>5463.59</v>
       </c>
     </row>
     <row r="517">
@@ -31988,7 +31988,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>32970.9</v>
+        <v>32781.51</v>
       </c>
     </row>
     <row r="518">
@@ -32049,7 +32049,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>10990.3</v>
+        <v>10927.17</v>
       </c>
     </row>
     <row r="519">
@@ -32110,7 +32110,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>2307.96</v>
+        <v>2294.71</v>
       </c>
     </row>
     <row r="520">
@@ -32171,7 +32171,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>10990.3</v>
+        <v>10927.17</v>
       </c>
     </row>
     <row r="521">
@@ -32232,7 +32232,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>3846.61</v>
+        <v>3824.51</v>
       </c>
     </row>
     <row r="522">
@@ -32293,7 +32293,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>37367.02</v>
+        <v>37152.38</v>
       </c>
     </row>
     <row r="523">
@@ -32354,7 +32354,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>5486.49</v>
+        <v>5454.97</v>
       </c>
     </row>
     <row r="524">
@@ -32415,7 +32415,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>2307.96</v>
+        <v>2294.71</v>
       </c>
     </row>
     <row r="525">
@@ -32476,7 +32476,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>9891.27</v>
+        <v>9834.450000000001</v>
       </c>
     </row>
     <row r="526">
@@ -32537,7 +32537,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>7847.07</v>
+        <v>7802</v>
       </c>
     </row>
     <row r="527">
@@ -32598,7 +32598,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>2615.69</v>
+        <v>2600.67</v>
       </c>
     </row>
     <row r="528">
@@ -32659,7 +32659,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>27475.75</v>
+        <v>27317.93</v>
       </c>
     </row>
     <row r="529">
@@ -32720,7 +32720,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>2304.67</v>
+        <v>2291.43</v>
       </c>
     </row>
     <row r="530">
@@ -32781,7 +32781,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>2747.58</v>
+        <v>2731.79</v>
       </c>
     </row>
     <row r="531">
@@ -32842,7 +32842,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>9891.27</v>
+        <v>9834.450000000001</v>
       </c>
     </row>
     <row r="532">
@@ -32903,7 +32903,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>5495.15</v>
+        <v>5463.59</v>
       </c>
     </row>
     <row r="533">
@@ -32964,7 +32964,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>3846.61</v>
+        <v>3824.51</v>
       </c>
     </row>
     <row r="534">
@@ -33025,7 +33025,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>4396.12</v>
+        <v>4370.87</v>
       </c>
     </row>
     <row r="535">
@@ -33086,7 +33086,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>10990.3</v>
+        <v>10927.17</v>
       </c>
     </row>
     <row r="536">
@@ -33147,7 +33147,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>2307.96</v>
+        <v>2294.71</v>
       </c>
     </row>
     <row r="537">
@@ -33208,7 +33208,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>3297.09</v>
+        <v>3278.15</v>
       </c>
     </row>
     <row r="538">
@@ -33269,7 +33269,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>3297.09</v>
+        <v>3278.15</v>
       </c>
     </row>
     <row r="539">
@@ -33330,7 +33330,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>7693.21</v>
+        <v>7649.02</v>
       </c>
     </row>
     <row r="540">
@@ -33391,7 +33391,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>2307.96</v>
+        <v>2294.71</v>
       </c>
     </row>
     <row r="541">
@@ -33452,7 +33452,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>8792.24</v>
+        <v>8741.74</v>
       </c>
     </row>
     <row r="542">
@@ -33513,7 +33513,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>13188.36</v>
+        <v>13112.6</v>
       </c>
     </row>
     <row r="543">
@@ -33574,7 +33574,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>5495.15</v>
+        <v>5463.59</v>
       </c>
     </row>
     <row r="544">
@@ -33635,7 +33635,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>32970.9</v>
+        <v>32781.51</v>
       </c>
     </row>
     <row r="545">
@@ -33696,7 +33696,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>22112.49</v>
+        <v>21985.47</v>
       </c>
     </row>
     <row r="546">
@@ -33757,7 +33757,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>10990.3</v>
+        <v>10927.17</v>
       </c>
     </row>
     <row r="547">
@@ -33818,7 +33818,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>12089.33</v>
+        <v>12019.89</v>
       </c>
     </row>
     <row r="548">
@@ -33879,7 +33879,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>3846.61</v>
+        <v>3824.51</v>
       </c>
     </row>
     <row r="549">
@@ -33940,7 +33940,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>16485.45</v>
+        <v>16390.76</v>
       </c>
     </row>
     <row r="550">
@@ -34001,7 +34001,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>10990.3</v>
+        <v>10919.89</v>
       </c>
     </row>
     <row r="551">
@@ -34062,7 +34062,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>2857.48</v>
+        <v>2839.17</v>
       </c>
     </row>
     <row r="552">
@@ -34123,7 +34123,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>3297.09</v>
+        <v>3275.97</v>
       </c>
     </row>
     <row r="553">
@@ -34184,7 +34184,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>43961.2</v>
+        <v>43679.57</v>
       </c>
     </row>
     <row r="554">
@@ -34245,7 +34245,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>5495.15</v>
+        <v>5459.95</v>
       </c>
     </row>
     <row r="555">
@@ -34306,7 +34306,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>2304.3</v>
+        <v>2289.54</v>
       </c>
     </row>
     <row r="556">
@@ -34367,7 +34367,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>2307.96</v>
+        <v>2293.18</v>
       </c>
     </row>
     <row r="557">
@@ -34428,7 +34428,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>5495.15</v>
+        <v>5459.95</v>
       </c>
     </row>
     <row r="558">
@@ -34489,7 +34489,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>7681.01</v>
+        <v>7631.8</v>
       </c>
     </row>
     <row r="559">
@@ -34550,7 +34550,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>7681.01</v>
+        <v>7631.8</v>
       </c>
     </row>
     <row r="560">
@@ -34611,7 +34611,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>2417.87</v>
+        <v>2402.38</v>
       </c>
     </row>
     <row r="561">
@@ -34672,7 +34672,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>11979.92</v>
+        <v>11903.17</v>
       </c>
     </row>
     <row r="562">
@@ -34733,7 +34733,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>32970.9</v>
+        <v>32759.68</v>
       </c>
     </row>
     <row r="563">
@@ -34794,7 +34794,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>4176.31</v>
+        <v>4149.56</v>
       </c>
     </row>
     <row r="564">
@@ -34855,7 +34855,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>32970.9</v>
+        <v>32759.68</v>
       </c>
     </row>
     <row r="565">
@@ -34916,7 +34916,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>7693.21</v>
+        <v>7643.92</v>
       </c>
     </row>
     <row r="566">
@@ -34977,7 +34977,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>2307.96</v>
+        <v>2293.18</v>
       </c>
     </row>
     <row r="567">
@@ -35038,7 +35038,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>3297.09</v>
+        <v>3275.97</v>
       </c>
     </row>
     <row r="568">
@@ -35099,7 +35099,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>2527.77</v>
+        <v>2511.58</v>
       </c>
     </row>
     <row r="569">
@@ -35160,7 +35160,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>10990.3</v>
+        <v>10919.89</v>
       </c>
     </row>
     <row r="570">
@@ -35221,7 +35221,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>15386.42</v>
+        <v>15287.85</v>
       </c>
     </row>
     <row r="571">
@@ -35282,7 +35282,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>4396.12</v>
+        <v>4367.96</v>
       </c>
     </row>
     <row r="572">
@@ -35343,7 +35343,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>2857.48</v>
+        <v>2839.17</v>
       </c>
     </row>
     <row r="573">
@@ -35404,7 +35404,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>6594.18</v>
+        <v>6551.94</v>
       </c>
     </row>
     <row r="574">
@@ -35465,7 +35465,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>2912.05</v>
+        <v>2893.39</v>
       </c>
     </row>
     <row r="575">
@@ -35526,7 +35526,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>27475.75</v>
+        <v>27299.73</v>
       </c>
     </row>
     <row r="576">
@@ -35587,7 +35587,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>3973.21</v>
+        <v>3947.75</v>
       </c>
     </row>
     <row r="577">
@@ -35648,7 +35648,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>37367.02</v>
+        <v>37127.63</v>
       </c>
     </row>
     <row r="578">
@@ -35709,7 +35709,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>10990.3</v>
+        <v>10919.89</v>
       </c>
     </row>
     <row r="579">
@@ -35770,7 +35770,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>7693.21</v>
+        <v>7643.92</v>
       </c>
     </row>
     <row r="580">
@@ -35831,7 +35831,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>37367.02</v>
+        <v>37127.63</v>
       </c>
     </row>
     <row r="581">
@@ -35892,7 +35892,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>3297.09</v>
+        <v>3275.97</v>
       </c>
     </row>
     <row r="582">
@@ -35953,7 +35953,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>10990.3</v>
+        <v>10919.89</v>
       </c>
     </row>
     <row r="583">
@@ -36014,7 +36014,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>2304.67</v>
+        <v>2289.9</v>
       </c>
     </row>
     <row r="584">
@@ -36075,7 +36075,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>5495.15</v>
+        <v>5459.95</v>
       </c>
     </row>
     <row r="585">
@@ -36136,7 +36136,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>2967.38</v>
+        <v>2948.37</v>
       </c>
     </row>
     <row r="586">
@@ -36197,7 +36197,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>2417.87</v>
+        <v>2402.38</v>
       </c>
     </row>
     <row r="587">
@@ -36258,7 +36258,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>10990.3</v>
+        <v>10919.89</v>
       </c>
     </row>
     <row r="588">
@@ -36319,7 +36319,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>2304.67</v>
+        <v>2289.9</v>
       </c>
     </row>
     <row r="589">
@@ -36380,7 +36380,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>2304.67</v>
+        <v>2289.9</v>
       </c>
     </row>
     <row r="590">
@@ -36441,7 +36441,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>2747.58</v>
+        <v>2729.97</v>
       </c>
     </row>
     <row r="591">
@@ -36502,7 +36502,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>4396.12</v>
+        <v>4367.96</v>
       </c>
     </row>
     <row r="592">
@@ -36563,7 +36563,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>4945.64</v>
+        <v>4913.95</v>
       </c>
     </row>
     <row r="593">
@@ -36624,7 +36624,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>2307.96</v>
+        <v>2293.18</v>
       </c>
     </row>
     <row r="594">
@@ -36685,7 +36685,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>6594.18</v>
+        <v>6551.94</v>
       </c>
     </row>
     <row r="595">
@@ -36746,7 +36746,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>5495.15</v>
+        <v>5459.95</v>
       </c>
     </row>
     <row r="596">
@@ -36807,7 +36807,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>6594.18</v>
+        <v>6551.94</v>
       </c>
     </row>
     <row r="597">
@@ -36868,7 +36868,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>8792.24</v>
+        <v>8735.91</v>
       </c>
     </row>
     <row r="598">
@@ -36929,7 +36929,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>21980.6</v>
+        <v>21839.78</v>
       </c>
     </row>
     <row r="599">
@@ -36990,7 +36990,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>10990.3</v>
+        <v>10919.89</v>
       </c>
     </row>
     <row r="600">
@@ -37051,7 +37051,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>16485.45</v>
+        <v>16379.84</v>
       </c>
     </row>
     <row r="601">
@@ -37112,7 +37112,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>2417.87</v>
+        <v>2402.38</v>
       </c>
     </row>
     <row r="602">
@@ -37173,7 +37173,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>14287.39</v>
+        <v>14195.86</v>
       </c>
     </row>
     <row r="603">
@@ -37234,7 +37234,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>5495.15</v>
+        <v>5459.95</v>
       </c>
     </row>
     <row r="604">
@@ -37295,7 +37295,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>5495.15</v>
+        <v>5459.95</v>
       </c>
     </row>
     <row r="605">
@@ -37356,7 +37356,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>5495.15</v>
+        <v>5459.95</v>
       </c>
     </row>
     <row r="606">
@@ -37417,7 +37417,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>10990.3</v>
+        <v>10919.89</v>
       </c>
     </row>
     <row r="607">
@@ -37478,7 +37478,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>4396.12</v>
+        <v>4367.96</v>
       </c>
     </row>
     <row r="608">
@@ -37539,7 +37539,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>2747.58</v>
+        <v>2729.97</v>
       </c>
     </row>
     <row r="609">
@@ -37600,7 +37600,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>7693.21</v>
+        <v>7643.92</v>
       </c>
     </row>
     <row r="610">
@@ -37661,7 +37661,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>2307.96</v>
+        <v>2293.18</v>
       </c>
     </row>
     <row r="611">
@@ -37722,7 +37722,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>3297.09</v>
+        <v>3275.97</v>
       </c>
     </row>
     <row r="612">
@@ -37783,7 +37783,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>3297.09</v>
+        <v>3275.97</v>
       </c>
     </row>
     <row r="613">
@@ -37844,7 +37844,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>2304.3</v>
+        <v>2294.38</v>
       </c>
     </row>
     <row r="614">
@@ -37905,7 +37905,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>2747.58</v>
+        <v>2735.74</v>
       </c>
     </row>
     <row r="615">
@@ -37966,7 +37966,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>6594.18</v>
+        <v>6565.77</v>
       </c>
     </row>
     <row r="616">
@@ -38027,7 +38027,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>4496.08</v>
+        <v>4476.71</v>
       </c>
     </row>
     <row r="617">
@@ -38088,7 +38088,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>14287.39</v>
+        <v>14225.84</v>
       </c>
     </row>
     <row r="618">
@@ -38149,7 +38149,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>2747.58</v>
+        <v>2735.74</v>
       </c>
     </row>
     <row r="619">
@@ -38210,7 +38210,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>3297.09</v>
+        <v>3282.89</v>
       </c>
     </row>
     <row r="620">
@@ -38271,7 +38271,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>3297.09</v>
+        <v>3282.89</v>
       </c>
     </row>
     <row r="621">
@@ -38332,7 +38332,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>2802.53</v>
+        <v>2790.45</v>
       </c>
     </row>
     <row r="622">
@@ -38393,7 +38393,7 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>3297.09</v>
+        <v>3282.89</v>
       </c>
     </row>
     <row r="623">
@@ -38454,7 +38454,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>5495.15</v>
+        <v>5471.48</v>
       </c>
     </row>
     <row r="624">
@@ -38515,7 +38515,7 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>3516.9</v>
+        <v>3501.75</v>
       </c>
     </row>
     <row r="625">
@@ -38576,7 +38576,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>2307.96</v>
+        <v>2298.02</v>
       </c>
     </row>
     <row r="626">
@@ -38637,7 +38637,7 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>2411.27</v>
+        <v>2400.88</v>
       </c>
     </row>
     <row r="627">
@@ -38698,7 +38698,7 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>3297.09</v>
+        <v>3282.89</v>
       </c>
     </row>
     <row r="628">
@@ -38759,7 +38759,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>12089.33</v>
+        <v>12037.25</v>
       </c>
     </row>
     <row r="629">
@@ -38820,7 +38820,7 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>10990.3</v>
+        <v>10942.95</v>
       </c>
     </row>
     <row r="630">
@@ -38881,7 +38881,7 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>9452.059999999999</v>
+        <v>9411.34</v>
       </c>
     </row>
     <row r="631">
@@ -38942,7 +38942,7 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>6594.18</v>
+        <v>6565.77</v>
       </c>
     </row>
     <row r="632">
@@ -39003,7 +39003,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>3297.09</v>
+        <v>3282.89</v>
       </c>
     </row>
     <row r="633">
@@ -39064,7 +39064,7 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>10990.3</v>
+        <v>10942.95</v>
       </c>
     </row>
     <row r="634">
@@ -39125,7 +39125,7 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>43961.2</v>
+        <v>43771.82</v>
       </c>
     </row>
     <row r="635">
@@ -39186,7 +39186,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>16485.45</v>
+        <v>16414.43</v>
       </c>
     </row>
     <row r="636">
@@ -39247,7 +39247,7 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>2307.96</v>
+        <v>2298.02</v>
       </c>
     </row>
     <row r="637">
@@ -39308,7 +39308,7 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>5495.15</v>
+        <v>5471.48</v>
       </c>
     </row>
     <row r="638">
@@ -39369,7 +39369,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>5783.1</v>
+        <v>5758.18</v>
       </c>
     </row>
     <row r="639">
@@ -39430,7 +39430,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>3297.09</v>
+        <v>3282.89</v>
       </c>
     </row>
     <row r="640">
@@ -39491,7 +39491,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>10990.3</v>
+        <v>10942.95</v>
       </c>
     </row>
     <row r="641">
@@ -39552,7 +39552,7 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>32970.9</v>
+        <v>32828.86</v>
       </c>
     </row>
     <row r="642">
@@ -39613,7 +39613,7 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>2307.96</v>
+        <v>2298.02</v>
       </c>
     </row>
     <row r="643">
@@ -39674,7 +39674,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>16485.45</v>
+        <v>16414.43</v>
       </c>
     </row>
     <row r="644">
@@ -39735,7 +39735,7 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>8792.24</v>
+        <v>8754.360000000001</v>
       </c>
     </row>
     <row r="645">
@@ -39796,7 +39796,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>4396.12</v>
+        <v>4377.18</v>
       </c>
     </row>
     <row r="646">
@@ -39857,7 +39857,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>10990.3</v>
+        <v>10942.95</v>
       </c>
     </row>
     <row r="647">
@@ -39918,7 +39918,7 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>14287.39</v>
+        <v>14225.84</v>
       </c>
     </row>
     <row r="648">
@@ -39979,7 +39979,7 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>3297.09</v>
+        <v>3282.89</v>
       </c>
     </row>
     <row r="649">
@@ -40040,7 +40040,7 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>2362.91</v>
+        <v>2352.74</v>
       </c>
     </row>
     <row r="650">
@@ -40101,7 +40101,7 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>8242.73</v>
+        <v>8207.219999999999</v>
       </c>
     </row>
     <row r="651">
@@ -40162,7 +40162,7 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>25277.69</v>
+        <v>25168.8</v>
       </c>
     </row>
     <row r="652">
@@ -40223,7 +40223,7 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>38466.05</v>
+        <v>38300.34</v>
       </c>
     </row>
     <row r="653">
@@ -40284,7 +40284,7 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>4945.64</v>
+        <v>4924.33</v>
       </c>
     </row>
     <row r="654">
@@ -40345,7 +40345,7 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>14946.81</v>
+        <v>14882.42</v>
       </c>
     </row>
     <row r="655">
@@ -40406,7 +40406,7 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>2747.58</v>
+        <v>2707.83</v>
       </c>
     </row>
     <row r="656">
@@ -40467,7 +40467,7 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>2747.58</v>
+        <v>2707.83</v>
       </c>
     </row>
     <row r="657">
@@ -40528,7 +40528,7 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>16485.45</v>
+        <v>16246.95</v>
       </c>
     </row>
     <row r="658">
@@ -40589,7 +40589,7 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>32970.9</v>
+        <v>32493.91</v>
       </c>
     </row>
     <row r="659">
@@ -40650,7 +40650,7 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>8792.24</v>
+        <v>8665.040000000001</v>
       </c>
     </row>
     <row r="660">
@@ -40711,7 +40711,7 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>16155.74</v>
+        <v>15922.01</v>
       </c>
     </row>
     <row r="661">
@@ -40772,7 +40772,7 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>23365.38</v>
+        <v>23027.35</v>
       </c>
     </row>
     <row r="662">
@@ -40833,7 +40833,7 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>16485.45</v>
+        <v>16246.95</v>
       </c>
     </row>
     <row r="663">
@@ -40894,7 +40894,7 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>6594.18</v>
+        <v>6498.78</v>
       </c>
     </row>
     <row r="664">
@@ -40955,7 +40955,7 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>10990.3</v>
+        <v>10831.3</v>
       </c>
     </row>
     <row r="665">
@@ -41016,7 +41016,7 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>2417.87</v>
+        <v>2382.89</v>
       </c>
     </row>
     <row r="666">
@@ -41077,7 +41077,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>2307.96</v>
+        <v>2274.57</v>
       </c>
     </row>
     <row r="667">
@@ -41138,7 +41138,7 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>5495.15</v>
+        <v>5415.65</v>
       </c>
     </row>
     <row r="668">
@@ -41199,7 +41199,7 @@
         </is>
       </c>
       <c r="M668" s="2" t="n">
-        <v>3934.53</v>
+        <v>3877.61</v>
       </c>
     </row>
     <row r="669">
@@ -41260,7 +41260,7 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>3767.25</v>
+        <v>3712.75</v>
       </c>
     </row>
     <row r="670">
@@ -41321,7 +41321,7 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>16485.45</v>
+        <v>16246.95</v>
       </c>
     </row>
     <row r="671">
@@ -41382,7 +41382,7 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>2527.77</v>
+        <v>2491.2</v>
       </c>
     </row>
     <row r="672">
@@ -41443,7 +41443,7 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>10990.3</v>
+        <v>10831.3</v>
       </c>
     </row>
     <row r="673">
@@ -41504,7 +41504,7 @@
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>21980.6</v>
+        <v>21662.6</v>
       </c>
     </row>
     <row r="674">
@@ -41565,7 +41565,7 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>21980.6</v>
+        <v>21662.6</v>
       </c>
     </row>
     <row r="675">
@@ -41626,7 +41626,7 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>2304.67</v>
+        <v>2271.32</v>
       </c>
     </row>
     <row r="676">
@@ -41687,7 +41687,7 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>2307.96</v>
+        <v>2274.57</v>
       </c>
     </row>
     <row r="677">
@@ -41748,7 +41748,7 @@
         </is>
       </c>
       <c r="M677" s="2" t="n">
-        <v>13188.36</v>
+        <v>12997.56</v>
       </c>
     </row>
     <row r="678">
@@ -41809,7 +41809,7 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>2304.3</v>
+        <v>2270.97</v>
       </c>
     </row>
     <row r="679">
@@ -41870,7 +41870,7 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>4945.64</v>
+        <v>4874.09</v>
       </c>
     </row>
     <row r="680">
@@ -41931,7 +41931,7 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>4396.12</v>
+        <v>4332.52</v>
       </c>
     </row>
     <row r="681">
@@ -41992,7 +41992,7 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>32970.9</v>
+        <v>32493.91</v>
       </c>
     </row>
     <row r="682">
@@ -42053,7 +42053,7 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>32970.9</v>
+        <v>32493.91</v>
       </c>
     </row>
     <row r="683">
@@ -42114,7 +42114,7 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>4396.12</v>
+        <v>4332.52</v>
       </c>
     </row>
     <row r="684">
@@ -42175,7 +42175,7 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>2379.4</v>
+        <v>2344.98</v>
       </c>
     </row>
     <row r="685">
@@ -42236,7 +42236,7 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>5099.5</v>
+        <v>5025.72</v>
       </c>
     </row>
     <row r="686">
@@ -42297,7 +42297,7 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>2747.58</v>
+        <v>2707.83</v>
       </c>
     </row>
     <row r="687">
@@ -42358,7 +42358,7 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>35976.75</v>
+        <v>35456.27</v>
       </c>
     </row>
     <row r="688">
@@ -42419,7 +42419,7 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>37092.27</v>
+        <v>36294.23</v>
       </c>
     </row>
     <row r="689">
@@ -42480,7 +42480,7 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>8792.24</v>
+        <v>8603.08</v>
       </c>
     </row>
     <row r="690">
@@ -42541,7 +42541,7 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>37639.58</v>
+        <v>36829.77</v>
       </c>
     </row>
     <row r="691">
@@ -42602,7 +42602,7 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>16485.45</v>
+        <v>16130.77</v>
       </c>
     </row>
     <row r="692">
@@ -42663,7 +42663,7 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>17584.48</v>
+        <v>17206.15</v>
       </c>
     </row>
     <row r="693">
@@ -42724,7 +42724,7 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>4396.12</v>
+        <v>4301.54</v>
       </c>
     </row>
     <row r="694">
@@ -42785,7 +42785,7 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>16485.45</v>
+        <v>16130.77</v>
       </c>
     </row>
     <row r="695">
@@ -42846,7 +42846,7 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>18798.91</v>
+        <v>18394.45</v>
       </c>
     </row>
     <row r="696">
@@ -42907,7 +42907,7 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>12089.33</v>
+        <v>11829.23</v>
       </c>
     </row>
     <row r="697">
@@ -42968,7 +42968,7 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>2312.81</v>
+        <v>2263.05</v>
       </c>
     </row>
     <row r="698">
@@ -43029,7 +43029,7 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>6594.18</v>
+        <v>6452.31</v>
       </c>
     </row>
     <row r="699">
@@ -43090,7 +43090,7 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>2304.3</v>
+        <v>2254.73</v>
       </c>
     </row>
     <row r="700">
@@ -43151,7 +43151,7 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>74960.92999999999</v>
+        <v>73348.14999999999</v>
       </c>
     </row>
     <row r="701">
@@ -43212,7 +43212,7 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>4396.12</v>
+        <v>4301.54</v>
       </c>
     </row>
     <row r="702">
@@ -43273,7 +43273,7 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>4121.36</v>
+        <v>4032.69</v>
       </c>
     </row>
     <row r="703">
@@ -43334,7 +43334,7 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>3297.09</v>
+        <v>3226.15</v>
       </c>
     </row>
     <row r="704">
@@ -43395,7 +43395,7 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>60446.65</v>
+        <v>59146.14</v>
       </c>
     </row>
     <row r="705">
@@ -43456,7 +43456,7 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>2747.58</v>
+        <v>2688.46</v>
       </c>
     </row>
     <row r="706">
@@ -43517,7 +43517,7 @@
         </is>
       </c>
       <c r="M706" s="2" t="n">
-        <v>7693.21</v>
+        <v>7527.69</v>
       </c>
     </row>
     <row r="707">
@@ -43578,7 +43578,7 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>4396.12</v>
+        <v>4301.54</v>
       </c>
     </row>
     <row r="708">
@@ -43639,7 +43639,7 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>16485.45</v>
+        <v>16130.77</v>
       </c>
     </row>
     <row r="709">
@@ -43700,7 +43700,7 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>16721.79</v>
+        <v>16362.02</v>
       </c>
     </row>
     <row r="710">
@@ -43761,7 +43761,7 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>4780.78</v>
+        <v>4677.92</v>
       </c>
     </row>
     <row r="711">
@@ -43822,7 +43822,7 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>21980.6</v>
+        <v>21507.69</v>
       </c>
     </row>
     <row r="712">
@@ -43883,7 +43883,7 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>4396.12</v>
+        <v>4301.54</v>
       </c>
     </row>
     <row r="713">
@@ -43944,7 +43944,7 @@
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>5385.25</v>
+        <v>5269.38</v>
       </c>
     </row>
     <row r="714">
@@ -44005,7 +44005,7 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>32970.9</v>
+        <v>32261.53</v>
       </c>
     </row>
     <row r="715">
@@ -44066,7 +44066,7 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>8727.950000000001</v>
+        <v>8540.17</v>
       </c>
     </row>
     <row r="716">
@@ -44127,7 +44127,7 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>2307.96</v>
+        <v>2258.31</v>
       </c>
     </row>
     <row r="717">
@@ -44188,7 +44188,7 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>7891.04</v>
+        <v>7721.26</v>
       </c>
     </row>
     <row r="718">
@@ -44249,7 +44249,7 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>14751.19</v>
+        <v>14433.82</v>
       </c>
     </row>
     <row r="719">
@@ -44310,7 +44310,7 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>6594.18</v>
+        <v>6452.31</v>
       </c>
     </row>
     <row r="720">
@@ -44371,7 +44371,7 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>26651.48</v>
+        <v>26078.07</v>
       </c>
     </row>
     <row r="721">
@@ -44432,7 +44432,7 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>2747.58</v>
+        <v>2688.46</v>
       </c>
     </row>
     <row r="722">
@@ -44493,7 +44493,7 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>43961.2</v>
+        <v>42938.27</v>
       </c>
     </row>
     <row r="723">
@@ -44554,7 +44554,7 @@
         </is>
       </c>
       <c r="M723" s="2" t="n">
-        <v>15386.42</v>
+        <v>15028.39</v>
       </c>
     </row>
     <row r="724">
@@ -44615,7 +44615,7 @@
         </is>
       </c>
       <c r="M724" s="2" t="n">
-        <v>10990.3</v>
+        <v>10734.57</v>
       </c>
     </row>
     <row r="725">
@@ -44676,7 +44676,7 @@
         </is>
       </c>
       <c r="M725" s="2" t="n">
-        <v>38371.54</v>
+        <v>37478.67</v>
       </c>
     </row>
     <row r="726">
@@ -44737,7 +44737,7 @@
         </is>
       </c>
       <c r="M726" s="2" t="n">
-        <v>3406.99</v>
+        <v>3327.72</v>
       </c>
     </row>
     <row r="727">
@@ -44798,7 +44798,7 @@
         </is>
       </c>
       <c r="M727" s="2" t="n">
-        <v>6044.67</v>
+        <v>5904.01</v>
       </c>
     </row>
     <row r="728">
@@ -44859,7 +44859,7 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>16485.45</v>
+        <v>16101.85</v>
       </c>
     </row>
     <row r="729">
@@ -44920,7 +44920,7 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>5495.15</v>
+        <v>5367.28</v>
       </c>
     </row>
     <row r="730">
@@ -44981,7 +44981,7 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>7693.21</v>
+        <v>7514.2</v>
       </c>
     </row>
     <row r="731">
@@ -45042,7 +45042,7 @@
         </is>
       </c>
       <c r="M731" s="2" t="n">
-        <v>41763.14</v>
+        <v>40791.35</v>
       </c>
     </row>
     <row r="732">
@@ -45103,7 +45103,7 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>3297.09</v>
+        <v>3220.37</v>
       </c>
     </row>
     <row r="733">
@@ -45164,7 +45164,7 @@
         </is>
       </c>
       <c r="M733" s="2" t="n">
-        <v>57517.81</v>
+        <v>56179.42</v>
       </c>
     </row>
     <row r="734">
@@ -45225,7 +45225,7 @@
         </is>
       </c>
       <c r="M734" s="2" t="n">
-        <v>6594.18</v>
+        <v>6440.74</v>
       </c>
     </row>
     <row r="735">
@@ -45286,7 +45286,7 @@
         </is>
       </c>
       <c r="M735" s="2" t="n">
-        <v>2747.58</v>
+        <v>2683.64</v>
       </c>
     </row>
     <row r="736">
@@ -45347,7 +45347,7 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>32970.9</v>
+        <v>32203.7</v>
       </c>
     </row>
     <row r="737">
@@ -45408,7 +45408,7 @@
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>3297.09</v>
+        <v>3220.37</v>
       </c>
     </row>
     <row r="738">
@@ -45469,7 +45469,7 @@
         </is>
       </c>
       <c r="M738" s="2" t="n">
-        <v>5506.14</v>
+        <v>5378.02</v>
       </c>
     </row>
     <row r="739">
@@ -45530,7 +45530,7 @@
         </is>
       </c>
       <c r="M739" s="2" t="n">
-        <v>9341.76</v>
+        <v>9124.379999999999</v>
       </c>
     </row>
     <row r="740">
@@ -45591,7 +45591,7 @@
         </is>
       </c>
       <c r="M740" s="2" t="n">
-        <v>4396.12</v>
+        <v>4293.83</v>
       </c>
     </row>
     <row r="741">
@@ -45652,7 +45652,7 @@
         </is>
       </c>
       <c r="M741" s="2" t="n">
-        <v>71436.96000000001</v>
+        <v>69774.67999999999</v>
       </c>
     </row>
     <row r="742">
@@ -45713,7 +45713,7 @@
         </is>
       </c>
       <c r="M742" s="2" t="n">
-        <v>8977.780000000001</v>
+        <v>8768.879999999999</v>
       </c>
     </row>
     <row r="743">
@@ -45774,7 +45774,7 @@
         </is>
       </c>
       <c r="M743" s="2" t="n">
-        <v>2747.58</v>
+        <v>2683.64</v>
       </c>
     </row>
     <row r="744">
@@ -45835,7 +45835,7 @@
         </is>
       </c>
       <c r="M744" s="2" t="n">
-        <v>13188.36</v>
+        <v>12881.48</v>
       </c>
     </row>
     <row r="745">
@@ -45896,7 +45896,7 @@
         </is>
       </c>
       <c r="M745" s="2" t="n">
-        <v>38466.05</v>
+        <v>37570.98</v>
       </c>
     </row>
     <row r="746">
@@ -45957,7 +45957,7 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>3297.09</v>
+        <v>3220.37</v>
       </c>
     </row>
     <row r="747">
@@ -46018,7 +46018,7 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>5495.15</v>
+        <v>5367.28</v>
       </c>
     </row>
     <row r="748">
@@ -46079,7 +46079,7 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>8698.82</v>
+        <v>8496.41</v>
       </c>
     </row>
     <row r="749">
@@ -46140,7 +46140,7 @@
         </is>
       </c>
       <c r="M749" s="2" t="n">
-        <v>10990.3</v>
+        <v>10734.57</v>
       </c>
     </row>
     <row r="750">
@@ -46201,7 +46201,7 @@
         </is>
       </c>
       <c r="M750" s="2" t="n">
-        <v>4089.21</v>
+        <v>3994.06</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/suministro-de-combustibles/mar-2026.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/mar-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC mar-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC mar-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15921,7 +15921,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -16104,7 +16104,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16958,7 +16958,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17263,7 +17263,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -18117,7 +18117,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18361,7 +18361,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18422,7 +18422,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18544,7 +18544,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -19047,7 +19047,7 @@
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -19524,7 +19524,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -19890,7 +19890,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -20134,7 +20134,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -20195,7 +20195,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -20317,7 +20317,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20378,7 +20378,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -20866,7 +20866,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -21110,7 +21110,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -21171,7 +21171,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -21720,7 +21720,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -22147,7 +22147,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -22452,7 +22452,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -22513,7 +22513,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -22818,7 +22818,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -22940,7 +22940,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -23123,7 +23123,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -23855,7 +23855,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -23977,7 +23977,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -24404,7 +24404,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -24587,7 +24587,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -25136,7 +25136,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -25319,7 +25319,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -25563,7 +25563,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -25624,7 +25624,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -26234,7 +26234,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -26478,7 +26478,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -26905,7 +26905,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -26966,7 +26966,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -27271,7 +27271,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -27698,7 +27698,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -27820,7 +27820,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -28186,7 +28186,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -28308,7 +28308,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -28857,7 +28857,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -30321,7 +30321,7 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -30382,7 +30382,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -30931,7 +30931,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -31785,7 +31785,7 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -31907,7 +31907,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -32456,7 +32456,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -33798,7 +33798,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -34103,7 +34103,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -34286,7 +34286,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -34591,7 +34591,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -34835,7 +34835,7 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -36726,7 +36726,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -36970,7 +36970,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -37092,7 +37092,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -37519,7 +37519,7 @@
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -37580,7 +37580,7 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -37641,7 +37641,7 @@
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -37824,7 +37824,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -37885,7 +37885,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -37946,7 +37946,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -38129,7 +38129,7 @@
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -38251,7 +38251,7 @@
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -38922,7 +38922,7 @@
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -39105,7 +39105,7 @@
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -39227,7 +39227,7 @@
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -39410,7 +39410,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -40081,7 +40081,7 @@
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -40569,7 +40569,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -40630,7 +40630,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -41301,7 +41301,7 @@
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -41545,7 +41545,7 @@
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -41789,7 +41789,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -41850,7 +41850,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -42033,7 +42033,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
@@ -42704,7 +42704,7 @@
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -43436,7 +43436,7 @@
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
@@ -43741,7 +43741,7 @@
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
@@ -44107,7 +44107,7 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
@@ -44290,7 +44290,7 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
@@ -44351,7 +44351,7 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
@@ -44534,7 +44534,7 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
@@ -45205,7 +45205,7 @@
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
@@ -45327,7 +45327,7 @@
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
@@ -46120,7 +46120,7 @@
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">

--- a/docs/oc-mensuales/suministro-de-combustibles/mar-2026.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/mar-2026.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Fresia - Salud</t>
+          <t>I MUNICIPALIDAD DE FRESIA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I.Municipalidad de Camarones</t>
+          <t>Ilustre Municipalidad de Camarones</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LITUECHE</t>
+          <t>Hospital de Litueche</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE PETORCA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PETORCA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GORBEA</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION COMUNAL DE SALUD- CORP MARIA PINTO </t>
+          <t>CORPORACION MUNICIPAL DE MARÍA PINTO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GORBEA</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SE</t>
+          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>I.Municipalidad de Camarones</t>
+          <t>Ilustre Municipalidad de Camarones</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>COMISION CHILENA DE ENERGIA NUCLEAR</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA LOS ANDES</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11036,7 +11036,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Municipalidad de Yerbas Buenas-Depto. Salud</t>
+          <t>Ilustre Municipalidad de Yerbas Buenas</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Municipalidad de Yerbas Buenas-Depto. Salud</t>
+          <t>Ilustre Municipalidad de Yerbas Buenas</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Región Metropolitana" - B Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -12622,7 +12622,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12805,7 +12805,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION COMUNAL DE EDUCACION - CORP MARIA PINTO </t>
+          <t>CORPORACION MUNICIPAL DE MARÍA PINTO</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE SAN NICOLAS - DEPTO. DE SALUD</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13171,7 +13171,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13354,7 +13354,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13415,7 +13415,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Los Alamos - Dpto Salud</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13720,7 +13720,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Retiro</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14269,7 +14269,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Maule</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PESCA</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PUBLICA DEL ACONCAGUA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ACONCAGUA</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -15001,7 +15001,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Santa Rosa</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA ROSA</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15245,7 +15245,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Santa Rosa</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA ROSA</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15916,7 +15916,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Contulmo - Educación</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16038,7 +16038,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16099,7 +16099,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16343,7 +16343,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16587,7 +16587,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -16709,7 +16709,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -16831,7 +16831,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -17502,7 +17502,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Retiro</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17868,7 +17868,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -17929,7 +17929,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -18356,7 +18356,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -18722,7 +18722,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Proyecto La Cisterna</t>
+          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNITARIA</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -19397,7 +19397,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -19458,7 +19458,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Proyecto La Cisterna</t>
+          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNITARIA</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -20312,7 +20312,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Yumbel - Depto. Educacion</t>
+          <t>I MUNICIPALIDAD DE YUMBEL</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -20434,7 +20434,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -21593,7 +21593,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>DIRECCION DE EDUCACION</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
@@ -21959,7 +21959,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Ñuble</t>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -22147,7 +22147,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -22513,7 +22513,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -22879,7 +22879,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -22935,7 +22935,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LITUECHE</t>
+          <t>Hospital de Litueche</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -22996,7 +22996,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Río Negro - Salud</t>
+          <t>I MUNICIPALIDAD DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -23301,7 +23301,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -24404,7 +24404,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -24582,7 +24582,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>I MUNICIPALIDAD DE LOTA</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -24887,7 +24887,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -24948,7 +24948,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -25060,7 +25060,7 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
@@ -25558,7 +25558,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -25802,7 +25802,7 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -27022,7 +27022,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>ADMINISTRACIÓN ADUANA DE ARICA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -27266,7 +27266,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>Departamento Comunal de Salud</t>
+          <t>I MUNICIPALIDAD DE TUCAPEL</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -27510,7 +27510,7 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>I.Municipalidad de San Pablo -Salud</t>
+          <t>I MUNICIPALIDAD DE SAN PABLO</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -27693,7 +27693,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUALQUI DEPARTAMENTO DE SALUD</t>
+          <t>I MUNICIPALIDAD DE HUALQUI</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
@@ -27815,7 +27815,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUALQUI DEPARTAMENTO DE SALUD</t>
+          <t>I MUNICIPALIDAD DE HUALQUI</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -27998,7 +27998,7 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>Departamento Administrativo de Salud Municipal.</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
@@ -28059,7 +28059,7 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LUMACO</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
@@ -28303,7 +28303,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>Dirección de Educación Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
@@ -28608,7 +28608,7 @@
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Trehuaco - Salud</t>
+          <t>I MUNICIPALIDAD DE TREHUACO</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
@@ -28730,7 +28730,7 @@
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
@@ -29096,7 +29096,7 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -29157,7 +29157,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -29218,7 +29218,7 @@
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE COQUIMBO SERPAT</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -29401,7 +29401,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>ESCUELA NAVAL "ARTURO PRAT"</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -29828,7 +29828,7 @@
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -30438,7 +30438,7 @@
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
@@ -30804,7 +30804,7 @@
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>Departamento Administrativo de Salud Municipal.</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
@@ -30926,7 +30926,7 @@
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO BIOBIO</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
@@ -31109,7 +31109,7 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GALVARINO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
@@ -31475,7 +31475,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Coyhaique</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
@@ -31536,12 +31536,12 @@
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -31597,12 +31597,12 @@
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -32451,7 +32451,7 @@
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
@@ -32512,7 +32512,7 @@
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H526" t="inlineStr">
@@ -32573,7 +32573,7 @@
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H527" t="inlineStr">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA METROPOLITANA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H535" t="inlineStr">
@@ -33183,7 +33183,7 @@
       </c>
       <c r="G537" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H537" t="inlineStr">
@@ -33488,7 +33488,7 @@
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
@@ -33915,7 +33915,7 @@
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA METROPOLITANA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
@@ -34342,7 +34342,7 @@
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>Departamento de Educación</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
@@ -34586,7 +34586,7 @@
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Penco - Salud</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
@@ -34647,7 +34647,7 @@
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
@@ -34891,7 +34891,7 @@
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H565" t="inlineStr">
@@ -35257,7 +35257,7 @@
       </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES AGROPECUARIAS</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H571" t="inlineStr">
@@ -35318,7 +35318,7 @@
       </c>
       <c r="G572" t="inlineStr">
         <is>
-          <t>Depto. Provincial Educación Valdivia</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H572" t="inlineStr">
@@ -35379,7 +35379,7 @@
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
@@ -35806,7 +35806,7 @@
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
@@ -35928,7 +35928,7 @@
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>Hospital de Ancud</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H582" t="inlineStr">
@@ -35989,7 +35989,7 @@
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H583" t="inlineStr">
@@ -36172,7 +36172,7 @@
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H586" t="inlineStr">
@@ -36416,7 +36416,7 @@
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Coyhaique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H590" t="inlineStr">
@@ -36538,7 +36538,7 @@
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GORBEA</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H592" t="inlineStr">
@@ -36721,7 +36721,7 @@
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONTULMO</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
@@ -37209,7 +37209,7 @@
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H603" t="inlineStr">
@@ -37331,7 +37331,7 @@
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H605" t="inlineStr">
@@ -37636,7 +37636,7 @@
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL F</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
         </is>
       </c>
       <c r="H610" t="inlineStr">
@@ -37880,7 +37880,7 @@
       </c>
       <c r="G614" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Concepción" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H614" t="inlineStr">
@@ -38246,7 +38246,7 @@
       </c>
       <c r="G620" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Contulmo - Salud</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H620" t="inlineStr">
@@ -38429,7 +38429,7 @@
       </c>
       <c r="G623" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H623" t="inlineStr">
@@ -38602,7 +38602,7 @@
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F626" t="inlineStr">
@@ -39100,7 +39100,7 @@
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>Dirección de Administración de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H634" t="inlineStr">
@@ -39161,7 +39161,7 @@
       </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LUMACO</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H635" t="inlineStr">
@@ -39283,7 +39283,7 @@
       </c>
       <c r="G637" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H637" t="inlineStr">
@@ -39466,7 +39466,7 @@
       </c>
       <c r="G640" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA LOS ANDES</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H640" t="inlineStr">
@@ -39527,7 +39527,7 @@
       </c>
       <c r="G641" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE QUILLÓN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H641" t="inlineStr">
@@ -40137,7 +40137,7 @@
       </c>
       <c r="G651" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H651" t="inlineStr">
@@ -40320,7 +40320,7 @@
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUELLON</t>
+          <t>Ilustre Municipalidad De Quellón</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
@@ -40381,7 +40381,7 @@
       </c>
       <c r="G655" t="inlineStr">
         <is>
-          <t>CONSULTORIO MIRAFLORES</t>
+          <t>Consultorio Miraflores</t>
         </is>
       </c>
       <c r="H655" t="inlineStr">
@@ -40869,7 +40869,7 @@
       </c>
       <c r="G663" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Quillon - Educación</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H663" t="inlineStr">
@@ -40991,7 +40991,7 @@
       </c>
       <c r="G665" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H665" t="inlineStr">
@@ -41418,7 +41418,7 @@
       </c>
       <c r="G672" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H672" t="inlineStr">
@@ -41540,7 +41540,7 @@
       </c>
       <c r="G674" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL DPTO ADMINIST</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H674" t="inlineStr">
@@ -41662,7 +41662,7 @@
       </c>
       <c r="G676" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H676" t="inlineStr">
@@ -41723,7 +41723,7 @@
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H677" t="inlineStr">
@@ -42089,7 +42089,7 @@
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H683" t="inlineStr">
@@ -42150,7 +42150,7 @@
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H684" t="inlineStr">
@@ -42211,7 +42211,7 @@
       </c>
       <c r="G685" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H685" t="inlineStr">
@@ -42272,7 +42272,7 @@
       </c>
       <c r="G686" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región de Atacama</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H686" t="inlineStr">
@@ -42943,7 +42943,7 @@
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H697" t="inlineStr">
@@ -43370,7 +43370,7 @@
       </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>Hospital de Quellón</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H704" t="inlineStr">
@@ -43924,7 +43924,7 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
@@ -44102,7 +44102,7 @@
       </c>
       <c r="G716" t="inlineStr">
         <is>
-          <t>CORPORACION DE EDUCACION, SALUD Y MENORES DE PUERT</t>
+          <t>Corporación de Ecuación, Salud y Menores de Puerto Natales</t>
         </is>
       </c>
       <c r="H716" t="inlineStr">
@@ -44224,7 +44224,7 @@
       </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H718" t="inlineStr">
@@ -44834,7 +44834,7 @@
       </c>
       <c r="G728" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NIQUEN</t>
+          <t>Ilustre Municipalidad de Ñiquen</t>
         </is>
       </c>
       <c r="H728" t="inlineStr">
@@ -44895,7 +44895,7 @@
       </c>
       <c r="G729" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H729" t="inlineStr">
@@ -45505,7 +45505,7 @@
       </c>
       <c r="G739" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H739" t="inlineStr">
@@ -45932,7 +45932,7 @@
       </c>
       <c r="G746" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE PUERTO MONTT</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H746" t="inlineStr">
@@ -45993,7 +45993,7 @@
       </c>
       <c r="G747" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE PUERTO MONTT</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H747" t="inlineStr">
@@ -46176,7 +46176,7 @@
       </c>
       <c r="G750" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION COMUNAL DE SALUD- CORP MARIA PINTO </t>
+          <t>CORPORACION MUNICIPAL DE MARÍA PINTO</t>
         </is>
       </c>
       <c r="H750" t="inlineStr">

--- a/docs/oc-mensuales/suministro-de-combustibles/mar-2026.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/mar-2026.xlsx
@@ -562,7 +562,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3747,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5047,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5112,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5242,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5307,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5372,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5437,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5502,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5567,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5632,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5697,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5827,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5957,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +6022,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6087,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6152,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6217,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6282,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6412,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6477,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6542,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6607,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6672,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6737,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6802,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6867,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6932,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6997,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +7062,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7127,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7192,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7257,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7322,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7387,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7452,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7517,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7582,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7647,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7712,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7777,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7842,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7972,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +8037,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +8102,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8167,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8232,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8297,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8427,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8492,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8557,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8622,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8687,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8817,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8882,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +9012,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +9077,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +9142,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9207,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9272,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9337,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9402,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9467,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9532,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9597,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9662,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9727,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9792,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9857,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9922,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9987,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +10052,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +10117,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10182,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10247,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10312,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10377,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10442,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10507,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10572,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10637,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10702,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10767,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10832,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10897,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10962,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +11027,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +11092,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +11157,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11222,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11287,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11352,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11417,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11482,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11547,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11612,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11677,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11742,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11807,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11872,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11937,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +12002,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +12067,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +12132,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +12197,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12262,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12327,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12392,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12457,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12522,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12587,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12652,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12717,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12782,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12847,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12912,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12977,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +13042,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +13107,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +13172,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +13237,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13302,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13367,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13432,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13497,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13562,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13692,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13757,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13822,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13952,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +14017,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +14082,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +14147,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +14212,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14277,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +14342,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14407,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14537,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14602,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14667,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14732,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14797,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14927,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14992,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +15057,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +15122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +15187,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +15252,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +15317,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15382,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15447,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15512,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15577,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15707,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15837,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15902,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15967,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +16032,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +16097,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +16162,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +16227,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +16292,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +16357,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16422,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16487,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16617,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16682,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16747,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16812,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16877,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +17007,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +17072,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +17137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +17202,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +17267,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +17332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +17397,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17462,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17527,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17592,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17657,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17722,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17787,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17917,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17982,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +18047,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +18112,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +18177,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +18242,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +18307,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +18372,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +18437,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +18502,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18567,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18632,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18697,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18762,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18827,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18957,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +19022,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +19087,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +19152,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +19217,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +19282,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +19347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +19412,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +19477,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19542,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19607,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19672,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19737,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19802,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19867,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19932,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19997,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +20062,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +20127,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +20192,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19110,7 +20322,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19171,7 +20387,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19232,7 +20452,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19293,7 +20517,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19354,7 +20582,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19415,7 +20647,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19476,7 +20712,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19537,7 +20777,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19598,7 +20842,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19659,7 +20907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19720,7 +20972,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19781,7 +21037,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19842,7 +21102,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19903,7 +21167,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19964,7 +21232,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20025,7 +21297,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20086,7 +21362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20147,7 +21427,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20208,7 +21492,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20269,7 +21557,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20330,7 +21622,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20391,7 +21687,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20452,7 +21752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20513,7 +21817,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20574,7 +21882,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20635,7 +21947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20696,7 +22012,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20757,7 +22077,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20818,7 +22142,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20879,7 +22207,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20940,7 +22272,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21001,7 +22337,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21062,7 +22402,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21123,7 +22467,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21184,7 +22532,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21245,7 +22597,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21306,7 +22662,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21367,7 +22727,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21428,7 +22792,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21489,7 +22857,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21550,7 +22922,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21611,7 +22987,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21672,7 +23052,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21733,7 +23117,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21794,7 +23182,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21855,7 +23247,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21916,7 +23312,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21977,7 +23377,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22038,7 +23442,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22099,7 +23507,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22160,7 +23572,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22221,7 +23637,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22282,7 +23702,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22343,7 +23767,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22404,7 +23832,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22465,7 +23897,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22526,7 +23962,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22587,7 +24027,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22648,7 +24092,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22709,7 +24157,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22770,7 +24222,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22831,7 +24287,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22892,7 +24352,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22953,7 +24417,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23014,7 +24482,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23075,7 +24547,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23136,7 +24612,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23197,7 +24677,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23258,7 +24742,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23319,7 +24807,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23380,7 +24872,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23441,7 +24937,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23502,7 +25002,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23563,7 +25067,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23624,7 +25132,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23685,7 +25197,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23746,7 +25262,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23807,7 +25327,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23868,7 +25392,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23929,7 +25457,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23990,7 +25522,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24051,7 +25587,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24112,7 +25652,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24173,7 +25717,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24234,7 +25782,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24295,7 +25847,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24356,7 +25912,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24417,7 +25977,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24478,7 +26042,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24539,7 +26107,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24600,7 +26172,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24661,7 +26237,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24722,7 +26302,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24783,7 +26367,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24844,7 +26432,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24905,7 +26497,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24966,7 +26562,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25027,7 +26627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25088,7 +26692,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25149,7 +26757,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25210,7 +26822,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25271,7 +26887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25332,7 +26952,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25393,7 +27017,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25454,7 +27082,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25515,7 +27147,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25576,7 +27212,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25637,7 +27277,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25698,7 +27342,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25759,7 +27407,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25820,7 +27472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25881,7 +27537,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25942,7 +27602,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26003,7 +27667,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26064,7 +27732,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26125,7 +27797,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26186,7 +27862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26247,7 +27927,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26308,7 +27992,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26369,7 +28057,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26430,7 +28122,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26491,7 +28187,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26552,7 +28252,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26613,7 +28317,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26674,7 +28382,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26735,7 +28447,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26796,7 +28512,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26857,7 +28577,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26918,7 +28642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26979,7 +28707,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27040,7 +28772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27101,7 +28837,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27162,7 +28902,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27223,7 +28967,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27284,7 +29032,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27345,7 +29097,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27406,7 +29162,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27467,7 +29227,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27528,7 +29292,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27589,7 +29357,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27650,7 +29422,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27711,7 +29487,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27772,7 +29552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27833,7 +29617,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27894,7 +29682,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27955,7 +29747,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28016,7 +29812,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28077,7 +29877,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28138,7 +29942,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28199,7 +30007,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28260,7 +30072,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28321,7 +30137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28382,7 +30202,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28443,7 +30267,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28504,7 +30332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28565,7 +30397,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28626,7 +30462,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28687,7 +30527,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28748,7 +30592,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28809,7 +30657,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28870,7 +30722,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28931,7 +30787,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28992,7 +30852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29053,7 +30917,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29114,7 +30982,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29175,7 +31047,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29236,7 +31112,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29297,7 +31177,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29358,7 +31242,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29419,7 +31307,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29480,7 +31372,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29541,7 +31437,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29602,7 +31502,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29663,7 +31567,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29724,7 +31632,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29785,7 +31697,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29846,7 +31762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29907,7 +31827,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29968,7 +31892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30029,7 +31957,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30090,7 +32022,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30151,7 +32087,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30212,7 +32152,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30273,7 +32217,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30334,7 +32282,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30395,7 +32347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30456,7 +32412,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30517,7 +32477,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30578,7 +32542,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30639,7 +32607,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30700,7 +32672,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30761,7 +32737,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30822,7 +32802,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30883,7 +32867,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30944,7 +32932,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31005,7 +32997,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31066,7 +33062,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31127,7 +33127,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31188,7 +33192,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31249,7 +33257,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31310,7 +33322,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31371,7 +33387,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31432,7 +33452,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31493,7 +33517,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31554,7 +33582,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31615,7 +33647,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31676,7 +33712,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31737,7 +33777,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31798,7 +33842,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31859,7 +33907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31920,7 +33972,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31981,7 +34037,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32042,7 +34102,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32103,7 +34167,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32164,7 +34232,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32225,7 +34297,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32286,7 +34362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32347,7 +34427,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32408,7 +34492,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32469,7 +34557,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32530,7 +34622,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32591,7 +34687,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32652,7 +34752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32713,7 +34817,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32774,7 +34882,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32835,7 +34947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32896,7 +35012,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32957,7 +35077,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33018,7 +35142,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33079,7 +35207,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33140,7 +35272,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33201,7 +35337,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33262,7 +35402,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33323,7 +35467,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33384,7 +35532,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33445,7 +35597,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33506,7 +35662,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33567,7 +35727,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33628,7 +35792,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33689,7 +35857,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33750,7 +35922,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33811,7 +35987,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33872,7 +36052,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33933,7 +36117,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33994,7 +36182,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34055,7 +36247,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34116,7 +36312,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34177,7 +36377,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34238,7 +36442,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34299,7 +36507,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34360,7 +36572,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34421,7 +36637,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34482,7 +36702,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34543,7 +36767,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34604,7 +36832,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34665,7 +36897,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34726,7 +36962,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34787,7 +37027,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34848,7 +37092,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34909,7 +37157,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34970,7 +37222,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35031,7 +37287,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35092,7 +37352,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35153,7 +37417,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35214,7 +37482,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35275,7 +37547,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35336,7 +37612,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr"/>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L572" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35397,7 +37677,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35458,7 +37742,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35519,7 +37807,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35580,7 +37872,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35641,7 +37937,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35702,7 +38002,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35763,7 +38067,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35824,7 +38132,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35885,7 +38197,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35946,7 +38262,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36007,7 +38327,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36068,7 +38392,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36129,7 +38457,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36190,7 +38522,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36251,7 +38587,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36312,7 +38652,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36373,7 +38717,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36434,7 +38782,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36495,7 +38847,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36556,7 +38912,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36617,7 +38977,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36678,7 +39042,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36739,7 +39107,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36800,7 +39172,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36861,7 +39237,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36922,7 +39302,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36983,7 +39367,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37044,7 +39432,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37105,7 +39497,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37166,7 +39562,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37227,7 +39627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37288,7 +39692,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37349,7 +39757,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37410,7 +39822,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37471,7 +39887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37532,7 +39952,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37593,7 +40017,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37654,7 +40082,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37715,7 +40147,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37776,7 +40212,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37837,7 +40277,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37898,7 +40342,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37959,7 +40407,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38020,7 +40472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38081,7 +40537,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L617" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38142,7 +40602,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38203,7 +40667,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38264,7 +40732,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38325,7 +40797,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38386,7 +40862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38447,7 +40927,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38508,7 +40992,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38569,7 +41057,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38630,7 +41122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38691,7 +41187,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38752,7 +41252,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38813,7 +41317,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38874,7 +41382,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38935,7 +41447,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38996,7 +41512,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39057,7 +41577,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39118,7 +41642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39179,7 +41707,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L635" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39240,7 +41772,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr"/>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L636" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39301,7 +41837,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39362,7 +41902,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39423,7 +41967,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39484,7 +42032,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39545,7 +42097,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39606,7 +42162,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39667,7 +42227,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39728,7 +42292,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39789,7 +42357,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39850,7 +42422,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39911,7 +42487,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39972,7 +42552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40033,7 +42617,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40094,7 +42682,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40155,7 +42747,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40216,7 +42812,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40277,7 +42877,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40338,7 +42942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40399,7 +43007,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40460,7 +43072,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40521,7 +43137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40582,7 +43202,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40643,7 +43267,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40704,7 +43332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40765,7 +43397,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40826,7 +43462,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40887,7 +43527,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40948,7 +43592,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41009,7 +43657,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41070,7 +43722,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41131,7 +43787,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41192,7 +43852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr"/>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L668" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41253,7 +43917,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K669" t="inlineStr"/>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L669" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41314,7 +43982,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41375,7 +44047,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L671" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41436,7 +44112,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L672" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41497,7 +44177,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41558,7 +44242,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41619,7 +44307,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L675" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41680,7 +44372,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L676" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41741,7 +44437,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L677" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41802,7 +44502,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K678" t="inlineStr"/>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L678" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41863,7 +44567,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41924,7 +44632,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K680" t="inlineStr"/>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L680" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41985,7 +44697,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L681" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42046,7 +44762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K682" t="inlineStr"/>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L682" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42107,7 +44827,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42168,7 +44892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K684" t="inlineStr"/>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L684" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42229,7 +44957,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K685" t="inlineStr"/>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L685" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42290,7 +45022,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L686" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42351,7 +45087,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K687" t="inlineStr"/>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L687" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42412,7 +45152,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L688" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42473,7 +45217,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K689" t="inlineStr"/>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L689" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42534,7 +45282,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K690" t="inlineStr"/>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L690" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42595,7 +45347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42656,7 +45412,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42717,7 +45477,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K693" t="inlineStr"/>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L693" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42778,7 +45542,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42839,7 +45607,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K695" t="inlineStr"/>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L695" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42900,7 +45672,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K696" t="inlineStr"/>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L696" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42961,7 +45737,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K697" t="inlineStr"/>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L697" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43022,7 +45802,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L698" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43083,7 +45867,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K699" t="inlineStr"/>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L699" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43144,7 +45932,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L700" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43205,7 +45997,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K701" t="inlineStr"/>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L701" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43266,7 +46062,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K702" t="inlineStr"/>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L702" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43327,7 +46127,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K703" t="inlineStr"/>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L703" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43388,7 +46192,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K704" t="inlineStr"/>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L704" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43449,7 +46257,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K705" t="inlineStr"/>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L705" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43510,7 +46322,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K706" t="inlineStr"/>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L706" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43571,7 +46387,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K707" t="inlineStr"/>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L707" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43632,7 +46452,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K708" t="inlineStr"/>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L708" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43693,7 +46517,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K709" t="inlineStr"/>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L709" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43754,7 +46582,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K710" t="inlineStr"/>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L710" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43815,7 +46647,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K711" t="inlineStr"/>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L711" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43876,7 +46712,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K712" t="inlineStr"/>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L712" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43937,7 +46777,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K713" t="inlineStr"/>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L713" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43998,7 +46842,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K714" t="inlineStr"/>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L714" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44059,7 +46907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K715" t="inlineStr"/>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L715" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44120,7 +46972,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K716" t="inlineStr"/>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L716" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44181,7 +47037,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K717" t="inlineStr"/>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L717" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44242,7 +47102,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K718" t="inlineStr"/>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L718" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44303,7 +47167,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K719" t="inlineStr"/>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L719" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44364,7 +47232,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K720" t="inlineStr"/>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L720" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44425,7 +47297,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K721" t="inlineStr"/>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L721" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44486,7 +47362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K722" t="inlineStr"/>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L722" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44547,7 +47427,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K723" t="inlineStr"/>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L723" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44608,7 +47492,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K724" t="inlineStr"/>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L724" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44669,7 +47557,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K725" t="inlineStr"/>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L725" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44730,7 +47622,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K726" t="inlineStr"/>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L726" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44791,7 +47687,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K727" t="inlineStr"/>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L727" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44852,7 +47752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K728" t="inlineStr"/>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L728" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44913,7 +47817,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K729" t="inlineStr"/>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L729" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44974,7 +47882,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K730" t="inlineStr"/>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L730" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45035,7 +47947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K731" t="inlineStr"/>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L731" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45096,7 +48012,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K732" t="inlineStr"/>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L732" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45157,7 +48077,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K733" t="inlineStr"/>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L733" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45218,7 +48142,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K734" t="inlineStr"/>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L734" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45279,7 +48207,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K735" t="inlineStr"/>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L735" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45340,7 +48272,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K736" t="inlineStr"/>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L736" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45401,7 +48337,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K737" t="inlineStr"/>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L737" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45462,7 +48402,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K738" t="inlineStr"/>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L738" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45523,7 +48467,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K739" t="inlineStr"/>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L739" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45584,7 +48532,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K740" t="inlineStr"/>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L740" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45645,7 +48597,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K741" t="inlineStr"/>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L741" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45706,7 +48662,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K742" t="inlineStr"/>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L742" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45767,7 +48727,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K743" t="inlineStr"/>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L743" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45828,7 +48792,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K744" t="inlineStr"/>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L744" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45889,7 +48857,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K745" t="inlineStr"/>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L745" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45950,7 +48922,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K746" t="inlineStr"/>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L746" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46011,7 +48987,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K747" t="inlineStr"/>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L747" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46072,7 +49052,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K748" t="inlineStr"/>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L748" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46133,7 +49117,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K749" t="inlineStr"/>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L749" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46194,7 +49182,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K750" t="inlineStr"/>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L750" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/suministro-de-combustibles/mar-2026.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/mar-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M750"/>
+  <dimension ref="A1:M751"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -794,7 +794,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -6969,7 +6969,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -15744,7 +15744,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -32254,7 +32254,7 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
@@ -44084,7 +44084,7 @@
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F672" t="inlineStr">
@@ -44129,7 +44129,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>3713-41-CM26</t>
+          <t>4881-18-CM26</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
@@ -44154,17 +44154,17 @@
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>65.511.520-k</t>
         </is>
       </c>
       <c r="G673" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -44188,13 +44188,13 @@
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>21662.6</v>
+        <v>2707.83</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>2762-210-CM26</t>
+          <t>3444-24-CM26</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
@@ -44214,22 +44214,22 @@
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>69.151.202-9</t>
+          <t>61.951.400-9</t>
         </is>
       </c>
       <c r="G674" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -44253,13 +44253,13 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>21662.6</v>
+        <v>5025.72</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>574-128-CM26</t>
+          <t>3444-25-CM26</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
@@ -44284,17 +44284,17 @@
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>61.606.610-2</t>
+          <t>61.951.400-9</t>
         </is>
       </c>
       <c r="G675" t="inlineStr">
         <is>
-          <t>DR. VICTOR HUGO MOLL DE CABILDO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
@@ -44318,13 +44318,13 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>2271.32</v>
+        <v>2344.98</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>4123-127-CM26</t>
+          <t>3683-46-CM26</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
@@ -44349,17 +44349,17 @@
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>69.140.302-5</t>
+          <t>69.080.800-5</t>
         </is>
       </c>
       <c r="G676" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NINHUE</t>
+          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
         </is>
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -44383,13 +44383,13 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>2274.57</v>
+        <v>32493.91</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>2793-255-CM26</t>
+          <t>3587-96-CM26</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
@@ -44409,22 +44409,22 @@
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>69.190.500-4</t>
         </is>
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>I MUNICIPALIDAD DE CARAHUE</t>
         </is>
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -44448,13 +44448,13 @@
         </is>
       </c>
       <c r="M677" s="2" t="n">
-        <v>12997.56</v>
+        <v>32493.91</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>1057543-598-CM26</t>
+          <t>4939-121-CM26</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
@@ -44474,37 +44474,37 @@
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>61.607.201-3</t>
+          <t>69.231.100-0</t>
         </is>
       </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD TALCAHUANO HOSPITAL DE</t>
+          <t>I MUNICIPALIDAD DE CHAITEN</t>
         </is>
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J678" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K678" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L678" t="inlineStr">
@@ -44513,13 +44513,13 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>2270.97</v>
+        <v>4332.52</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>4738-71-CM26</t>
+          <t>1230848-44-CM26</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
@@ -44539,22 +44539,22 @@
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G679" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -44578,13 +44578,13 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>4874.09</v>
+        <v>4332.52</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>4939-121-CM26</t>
+          <t>1057543-598-CM26</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
@@ -44609,32 +44609,32 @@
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>69.231.100-0</t>
+          <t>61.607.201-3</t>
         </is>
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHAITEN</t>
+          <t>SERVICIO DE SALUD TALCAHUANO HOSPITAL DE</t>
         </is>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J680" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K680" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L680" t="inlineStr">
@@ -44643,13 +44643,13 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>4332.52</v>
+        <v>2270.97</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>3587-96-CM26</t>
+          <t>2793-255-CM26</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
@@ -44669,22 +44669,22 @@
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>69.190.500-4</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARAHUE</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -44708,13 +44708,13 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>32493.91</v>
+        <v>12997.56</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>3683-46-CM26</t>
+          <t>4123-127-CM26</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
@@ -44739,17 +44739,17 @@
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>69.080.800-5</t>
+          <t>69.140.302-5</t>
         </is>
       </c>
       <c r="G682" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -44773,13 +44773,13 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>32493.91</v>
+        <v>2274.57</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>1230848-44-CM26</t>
+          <t>574-128-CM26</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
@@ -44799,22 +44799,22 @@
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>61.606.610-2</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social de Calama</t>
+          <t>DR. VICTOR HUGO MOLL DE CABILDO</t>
         </is>
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -44838,13 +44838,13 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>4332.52</v>
+        <v>2271.32</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>3444-25-CM26</t>
+          <t>2762-210-CM26</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
@@ -44864,22 +44864,22 @@
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>61.951.400-9</t>
+          <t>69.151.202-9</t>
         </is>
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE CORONEL</t>
         </is>
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -44903,13 +44903,13 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>2344.98</v>
+        <v>21662.6</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>3444-24-CM26</t>
+          <t>3713-41-CM26</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
@@ -44934,17 +44934,17 @@
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>61.951.400-9</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G685" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -44968,13 +44968,13 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>5025.72</v>
+        <v>21662.6</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>4881-18-CM26</t>
+          <t>4738-71-CM26</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
@@ -44999,17 +44999,17 @@
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>65.511.520-k</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I686" t="inlineStr">
@@ -45033,7 +45033,7 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>2707.83</v>
+        <v>4874.09</v>
       </c>
     </row>
     <row r="687">
@@ -45104,7 +45104,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>2328-275-CM26</t>
+          <t>1057531-134-CM26</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
@@ -45124,17 +45124,17 @@
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.602.262-8</t>
         </is>
       </c>
       <c r="G688" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H688" t="inlineStr">
@@ -45163,13 +45163,13 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>36294.23</v>
+        <v>11829.23</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>4099-155-CM26</t>
+          <t>1660-210-CM26</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
@@ -45189,22 +45189,22 @@
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>69.073.300-5</t>
+          <t>61.606.408-8</t>
         </is>
       </c>
       <c r="G689" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA PINTO</t>
+          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
         </is>
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -45228,13 +45228,13 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>8603.08</v>
+        <v>4032.69</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>1736-315-CM26</t>
+          <t>1057506-3859-CM26</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
@@ -45259,17 +45259,17 @@
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>69.255.300-4</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA COMUNA DE EL BOSQUE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -45293,13 +45293,13 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>36829.77</v>
+        <v>4301.54</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>3501-65-CM26</t>
+          <t>720-97-CM26</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
@@ -45324,17 +45324,17 @@
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>69.081.700-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G691" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTA DE TILCOCO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
@@ -45358,13 +45358,13 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>16130.77</v>
+        <v>73348.14999999999</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>1493-225-CM26</t>
+          <t>1057506-3860-CM26</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
@@ -45384,17 +45384,17 @@
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>69.140.800-0</t>
+          <t>61.602.194-K</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
         </is>
       </c>
       <c r="H692" t="inlineStr">
@@ -45423,13 +45423,13 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>17206.15</v>
+        <v>2254.73</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>3656-191-CM26</t>
+          <t>1663-307-CM26</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
@@ -45449,22 +45449,22 @@
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>69.081.300-9</t>
+          <t>61.602.276-8</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE REQUINOA</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -45488,13 +45488,13 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>4301.54</v>
+        <v>59146.14</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>5520-1872-CM26</t>
+          <t>720-98-CM26</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
@@ -45519,17 +45519,17 @@
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G694" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
@@ -45553,13 +45553,13 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>16130.77</v>
+        <v>18394.45</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>720-98-CM26</t>
+          <t>2328-275-CM26</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
@@ -45579,22 +45579,22 @@
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G695" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I695" t="inlineStr">
@@ -45618,13 +45618,13 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>18394.45</v>
+        <v>36294.23</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>1057531-134-CM26</t>
+          <t>3656-191-CM26</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
@@ -45644,22 +45644,22 @@
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>61.602.262-8</t>
+          <t>69.081.300-9</t>
         </is>
       </c>
       <c r="G696" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
+          <t>I MUNICIPALIDAD DE REQUINOA</t>
         </is>
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
@@ -45683,13 +45683,13 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>11829.23</v>
+        <v>4301.54</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>2310-171-CM26</t>
+          <t>1493-225-CM26</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
@@ -45709,22 +45709,22 @@
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>69.110.100-2</t>
+          <t>69.140.800-0</t>
         </is>
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
@@ -45748,13 +45748,13 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>2263.05</v>
+        <v>17206.15</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>4519-134-CM26</t>
+          <t>3501-65-CM26</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
@@ -45774,22 +45774,22 @@
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>69.250.600-6</t>
+          <t>69.081.700-4</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TREHUACO</t>
+          <t>I MUNICIPALIDAD DE QUINTA DE TILCOCO</t>
         </is>
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
@@ -45813,13 +45813,13 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>6452.31</v>
+        <v>16130.77</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>1057506-3860-CM26</t>
+          <t>1736-315-CM26</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
@@ -45844,17 +45844,17 @@
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>69.255.300-4</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>I MUNICIPALIDAD DE LA COMUNA DE EL BOSQUE</t>
         </is>
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -45878,13 +45878,13 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>2254.73</v>
+        <v>36829.77</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>720-97-CM26</t>
+          <t>4099-155-CM26</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
@@ -45904,22 +45904,22 @@
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.073.300-5</t>
         </is>
       </c>
       <c r="G700" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE MARIA PINTO</t>
         </is>
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
@@ -45943,13 +45943,13 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>73348.14999999999</v>
+        <v>8603.08</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>1057506-3859-CM26</t>
+          <t>951-10-CM26</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
@@ -45974,17 +45974,17 @@
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>61.602.194-K</t>
+          <t>60.511.010-K</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COELEMU</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
         </is>
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
@@ -46008,13 +46008,13 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>4301.54</v>
+        <v>3226.15</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>1660-210-CM26</t>
+          <t>2310-171-CM26</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
@@ -46039,17 +46039,17 @@
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>61.606.408-8</t>
+          <t>69.110.100-2</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I702" t="inlineStr">
@@ -46073,13 +46073,13 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>4032.69</v>
+        <v>2263.05</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>951-10-CM26</t>
+          <t>5520-1872-CM26</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
@@ -46104,17 +46104,17 @@
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>60.511.010-K</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE TARAPACÁ</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
@@ -46138,13 +46138,13 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>3226.15</v>
+        <v>16130.77</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>1663-307-CM26</t>
+          <t>3596-234-CM26</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
@@ -46164,22 +46164,22 @@
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>61.602.276-8</t>
+          <t>69.050.300-K</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>I MUNICIPALIDAD DE PAPUDO</t>
         </is>
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I704" t="inlineStr">
@@ -46203,13 +46203,13 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>59146.14</v>
+        <v>7527.69</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>2785-199-CM26</t>
+          <t>4519-134-CM26</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
@@ -46234,17 +46234,17 @@
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>69.264.800-5</t>
+          <t>69.250.600-6</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
+          <t>I MUNICIPALIDAD DE TREHUACO</t>
         </is>
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
@@ -46268,13 +46268,13 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>2688.46</v>
+        <v>6452.31</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>3596-234-CM26</t>
+          <t>4179-304-CM26</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
@@ -46294,22 +46294,22 @@
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>69.050.300-K</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAPUDO</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I706" t="inlineStr">
@@ -46333,13 +46333,13 @@
         </is>
       </c>
       <c r="M706" s="2" t="n">
-        <v>7527.69</v>
+        <v>2688.46</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>1087-50-CM26</t>
+          <t>2785-199-CM26</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -46359,22 +46359,22 @@
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.264.800-5</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I707" t="inlineStr">
@@ -46398,13 +46398,13 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>4301.54</v>
+        <v>2688.46</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>1393093-350-CM26</t>
+          <t>1087-50-CM26</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
@@ -46429,17 +46429,17 @@
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
@@ -46463,13 +46463,13 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>16130.77</v>
+        <v>4301.54</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>1274189-104-CM26</t>
+          <t>1393093-350-CM26</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -46494,17 +46494,17 @@
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>70.934.900-7</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
         <is>
-          <t>CORPORACION DE DESARROLLO SOCIAL DE BUIN</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I709" t="inlineStr">
@@ -46528,13 +46528,13 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>16362.02</v>
+        <v>16130.77</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>557639-369-CM26</t>
+          <t>1274189-104-CM26</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
@@ -46554,22 +46554,22 @@
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>71.014.200-9</t>
+          <t>70.934.900-7</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
+          <t>CORPORACION DE DESARROLLO SOCIAL DE BUIN</t>
         </is>
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
@@ -46593,13 +46593,13 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>4677.92</v>
+        <v>16362.02</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>3666-9-CM26</t>
+          <t>1057539-2263-CM26</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
@@ -46619,22 +46619,22 @@
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>69.071.600-3</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIL TIL</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
@@ -46658,13 +46658,13 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>21507.69</v>
+        <v>68125.60000000001</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>809-27-CM26</t>
+          <t>557639-369-CM26</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
@@ -46684,22 +46684,22 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>71.014.200-9</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
         </is>
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
@@ -46723,13 +46723,13 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>4301.54</v>
+        <v>4677.92</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>1428662-30-CM26</t>
+          <t>3666-9-CM26</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
@@ -46749,37 +46749,37 @@
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>71.160.900-8</t>
+          <t>69.071.600-3</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUQUELDON PARA LA EDUC</t>
+          <t>I MUNICIPALIDAD DE TIL TIL</t>
         </is>
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K713" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L713" t="inlineStr">
@@ -46788,13 +46788,13 @@
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>5269.38</v>
+        <v>21507.69</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>434-134-CM26</t>
+          <t>1428662-30-CM26</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
@@ -46819,32 +46819,32 @@
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>69.120.400-6</t>
+          <t>71.160.900-8</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CAUQUENES</t>
+          <t>CORP MUNICIPAL DE PUQUELDON PARA LA EDUC</t>
         </is>
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K714" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L714" t="inlineStr">
@@ -46853,13 +46853,13 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>32261.53</v>
+        <v>5269.38</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>830715-31-CM26</t>
+          <t>3637-87-CM26</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
@@ -46879,37 +46879,37 @@
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>60.511.139-4</t>
+          <t>69.251.500-5</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN GREGORIO</t>
         </is>
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K715" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L715" t="inlineStr">
@@ -46918,13 +46918,13 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>8540.17</v>
+        <v>26078.07</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>1239966-109-CM26</t>
+          <t>434-134-CM26</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
@@ -46949,17 +46949,17 @@
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>71.165.800-9</t>
+          <t>69.120.400-6</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
         <is>
-          <t>Corporación de Ecuación, Salud y Menores de Puerto Natales</t>
+          <t>I MUNICIPALIDAD DE CAUQUENES</t>
         </is>
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
@@ -46983,13 +46983,13 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>2258.31</v>
+        <v>32261.53</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>3884-169-CM26</t>
+          <t>830715-31-CM26</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
@@ -47009,22 +47009,22 @@
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>69.040.600-4</t>
+          <t>60.511.139-4</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PAIHUANO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE PARINACOTA</t>
         </is>
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
@@ -47048,13 +47048,13 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>7721.26</v>
+        <v>8540.17</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>1432083-527-CM26</t>
+          <t>1239966-109-CM26</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
@@ -47074,37 +47074,37 @@
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>61.981.110-0</t>
+          <t>71.165.800-9</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
+          <t>Corporación de Ecuación, Salud y Menores de Puerto Natales</t>
         </is>
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K718" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L718" t="inlineStr">
@@ -47113,13 +47113,13 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>14433.82</v>
+        <v>2258.31</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>3734-223-CM26</t>
+          <t>3884-169-CM26</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
@@ -47139,22 +47139,22 @@
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>69.170.300-2</t>
+          <t>69.040.600-4</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAJA</t>
+          <t>I MUNICIPALIDAD PAIHUANO</t>
         </is>
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
@@ -47178,13 +47178,13 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>6452.31</v>
+        <v>7721.26</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>3637-87-CM26</t>
+          <t>1432083-527-CM26</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
@@ -47209,17 +47209,17 @@
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>69.251.500-5</t>
+          <t>61.981.110-0</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN GREGORIO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
@@ -47243,13 +47243,13 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>26078.07</v>
+        <v>14433.82</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>4179-304-CM26</t>
+          <t>809-27-CM26</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
@@ -47274,12 +47274,12 @@
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H721" t="inlineStr">
@@ -47308,13 +47308,13 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>2688.46</v>
+        <v>4301.54</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>3568-257-CM26</t>
+          <t>3734-223-CM26</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
@@ -47329,7 +47329,7 @@
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
@@ -47339,17 +47339,17 @@
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>69.201.200-3</t>
+          <t>69.170.300-2</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
+          <t>I MUNICIPALIDAD DE LAJA</t>
         </is>
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
@@ -47373,13 +47373,13 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>42938.27</v>
+        <v>6452.31</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>4236-181-CM26</t>
+          <t>3568-257-CM26</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
@@ -47404,17 +47404,17 @@
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>69.160.200-1</t>
+          <t>69.201.200-3</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
+          <t>I MUNICIPALIDAD DE PANGUIPULLI</t>
         </is>
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
@@ -47438,13 +47438,13 @@
         </is>
       </c>
       <c r="M723" s="2" t="n">
-        <v>15028.39</v>
+        <v>42938.27</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>2548-170-CM26</t>
+          <t>4236-181-CM26</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
@@ -47469,32 +47469,32 @@
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>69.160.200-1</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J724" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K724" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L724" t="inlineStr">
@@ -47503,13 +47503,13 @@
         </is>
       </c>
       <c r="M724" s="2" t="n">
-        <v>10734.57</v>
+        <v>15028.39</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>4062-216-CM26</t>
+          <t>2548-170-CM26</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
@@ -47529,37 +47529,37 @@
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>69.200.400-0</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIQUINA</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K725" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L725" t="inlineStr">
@@ -47568,13 +47568,13 @@
         </is>
       </c>
       <c r="M725" s="2" t="n">
-        <v>37478.67</v>
+        <v>10734.57</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>1770-8-CM26</t>
+          <t>4062-216-CM26</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
@@ -47599,17 +47599,17 @@
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.200.400-0</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE MARIQUINA</t>
         </is>
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
@@ -47633,13 +47633,13 @@
         </is>
       </c>
       <c r="M726" s="2" t="n">
-        <v>3327.72</v>
+        <v>37478.67</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>2908-75-CM26</t>
+          <t>1770-8-CM26</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
@@ -47664,17 +47664,17 @@
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>69.200.300-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LANCO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
@@ -47698,13 +47698,13 @@
         </is>
       </c>
       <c r="M727" s="2" t="n">
-        <v>5904.01</v>
+        <v>3327.72</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>4329-184-CM26</t>
+          <t>2908-75-CM26</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
@@ -47724,22 +47724,22 @@
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>69.140.600-8</t>
+          <t>69.200.300-4</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Ñiquen</t>
+          <t>I MUNICIPALIDAD DE LANCO</t>
         </is>
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
@@ -47763,13 +47763,13 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>16101.85</v>
+        <v>5904.01</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>4906-83-CM26</t>
+          <t>4329-184-CM26</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
@@ -47789,22 +47789,22 @@
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>61.980.740-5</t>
+          <t>69.140.600-8</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>Ilustre Municipalidad de Ñiquen</t>
         </is>
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
@@ -47828,13 +47828,13 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>5367.28</v>
+        <v>16101.85</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>3707-187-CM26</t>
+          <t>4906-83-CM26</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
@@ -47859,17 +47859,17 @@
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>61.980.740-5</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
@@ -47893,13 +47893,13 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>7514.2</v>
+        <v>5367.28</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>377-138-CM26</t>
+          <t>3707-187-CM26</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
@@ -47924,17 +47924,17 @@
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I731" t="inlineStr">
@@ -47958,13 +47958,13 @@
         </is>
       </c>
       <c r="M731" s="2" t="n">
-        <v>40791.35</v>
+        <v>7514.2</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>6-50-CM26</t>
+          <t>377-138-CM26</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
@@ -47989,17 +47989,17 @@
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>61.838.000-9</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION I REGION</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
@@ -48023,13 +48023,13 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>3220.37</v>
+        <v>40791.35</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>906-78-CM26</t>
+          <t>6-50-CM26</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
@@ -48054,17 +48054,17 @@
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.838.000-9</t>
         </is>
       </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION I REGION</t>
         </is>
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
@@ -48088,13 +48088,13 @@
         </is>
       </c>
       <c r="M733" s="2" t="n">
-        <v>56179.42</v>
+        <v>3220.37</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>4462-155-CM26</t>
+          <t>906-78-CM26</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
@@ -48119,17 +48119,17 @@
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
@@ -48153,13 +48153,13 @@
         </is>
       </c>
       <c r="M734" s="2" t="n">
-        <v>6440.74</v>
+        <v>56179.42</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>4179-306-CM26</t>
+          <t>4462-155-CM26</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
@@ -48184,17 +48184,17 @@
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
@@ -48218,13 +48218,13 @@
         </is>
       </c>
       <c r="M735" s="2" t="n">
-        <v>2683.64</v>
+        <v>6440.74</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>654-103-CM26</t>
+          <t>4179-306-CM26</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
@@ -48249,17 +48249,17 @@
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>61.820.004-3</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
@@ -48283,13 +48283,13 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>32203.7</v>
+        <v>2683.64</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>636811-70-CM26</t>
+          <t>654-103-CM26</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
@@ -48314,17 +48314,17 @@
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>61.606.908-k</t>
+          <t>61.820.004-3</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGIÓN DEL BIO BIO</t>
         </is>
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
@@ -48348,13 +48348,13 @@
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>3220.37</v>
+        <v>32203.7</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>2445-1801-CM26</t>
+          <t>636811-70-CM26</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
@@ -48379,12 +48379,12 @@
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>61.606.908-k</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
         </is>
       </c>
       <c r="H738" t="inlineStr">
@@ -48413,13 +48413,13 @@
         </is>
       </c>
       <c r="M738" s="2" t="n">
-        <v>5378.02</v>
+        <v>3220.37</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>3507-232-CM26</t>
+          <t>2445-1801-CM26</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
@@ -48439,22 +48439,22 @@
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>65.321.890-7</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G739" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALBUCO</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
@@ -48478,13 +48478,13 @@
         </is>
       </c>
       <c r="M739" s="2" t="n">
-        <v>9124.379999999999</v>
+        <v>5378.02</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>1057388-137-CM26</t>
+          <t>3507-232-CM26</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
@@ -48504,22 +48504,22 @@
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>61.602.224-5</t>
+          <t>65.321.890-7</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL PUREN</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
@@ -48543,13 +48543,13 @@
         </is>
       </c>
       <c r="M740" s="2" t="n">
-        <v>4293.83</v>
+        <v>9124.379999999999</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>2385-197-CM26</t>
+          <t>1057388-137-CM26</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
@@ -48569,37 +48569,37 @@
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>61.602.224-5</t>
         </is>
       </c>
       <c r="G741" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL PUREN</t>
         </is>
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J741" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K741" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L741" t="inlineStr">
@@ -48608,13 +48608,13 @@
         </is>
       </c>
       <c r="M741" s="2" t="n">
-        <v>69774.67999999999</v>
+        <v>4293.83</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>3447-864-CM26</t>
+          <t>2385-197-CM26</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
@@ -48639,32 +48639,32 @@
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G742" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J742" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K742" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L742" t="inlineStr">
@@ -48673,13 +48673,13 @@
         </is>
       </c>
       <c r="M742" s="2" t="n">
-        <v>8768.879999999999</v>
+        <v>69774.67999999999</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>4179-305-CM26</t>
+          <t>3447-864-CM26</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
@@ -48704,17 +48704,17 @@
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G743" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I743" t="inlineStr">
@@ -48738,13 +48738,13 @@
         </is>
       </c>
       <c r="M743" s="2" t="n">
-        <v>2683.64</v>
+        <v>8768.879999999999</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>1049-546-CM26</t>
+          <t>4179-305-CM26</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
@@ -48764,22 +48764,22 @@
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>61.310.000-8</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G744" t="inlineStr">
         <is>
-          <t>INSTITUTO DE FOMENTO PESQUERO</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I744" t="inlineStr">
@@ -48803,13 +48803,13 @@
         </is>
       </c>
       <c r="M744" s="2" t="n">
-        <v>12881.48</v>
+        <v>2683.64</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>2694-40-CM26</t>
+          <t>1049-546-CM26</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
@@ -48834,12 +48834,12 @@
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>61.310.000-8</t>
         </is>
       </c>
       <c r="G745" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>INSTITUTO DE FOMENTO PESQUERO</t>
         </is>
       </c>
       <c r="H745" t="inlineStr">
@@ -48868,13 +48868,13 @@
         </is>
       </c>
       <c r="M745" s="2" t="n">
-        <v>37570.98</v>
+        <v>12881.48</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>815-17-CM26</t>
+          <t>2694-40-CM26</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
@@ -48894,22 +48894,22 @@
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>60.804.014-5</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G746" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H746" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I746" t="inlineStr">
@@ -48933,13 +48933,13 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>3220.37</v>
+        <v>37570.98</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>815-16-CM26</t>
+          <t>815-17-CM26</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
@@ -48998,13 +48998,13 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>5367.28</v>
+        <v>3220.37</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>3707-188-CM26</t>
+          <t>815-16-CM26</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
@@ -49029,17 +49029,17 @@
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>60.804.014-5</t>
         </is>
       </c>
       <c r="G748" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I748" t="inlineStr">
@@ -49063,13 +49063,13 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>8496.41</v>
+        <v>5367.28</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>2102-243-CM26</t>
+          <t>3707-188-CM26</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
@@ -49094,17 +49094,17 @@
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>61.602.212-1</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G749" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
@@ -49128,71 +49128,136 @@
         </is>
       </c>
       <c r="M749" s="2" t="n">
-        <v>10734.57</v>
+        <v>8496.41</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
+          <t>2102-243-CM26</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>61.602.212-1</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M750" s="2" t="n">
+        <v>10734.57</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
           <t>1389585-56-CM26</t>
         </is>
       </c>
-      <c r="B750" t="inlineStr">
-        <is>
-          <t>2239-13-LR25</t>
-        </is>
-      </c>
-      <c r="C750" t="inlineStr">
-        <is>
-          <t>mar-2026</t>
-        </is>
-      </c>
-      <c r="D750" t="inlineStr">
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="E750" t="inlineStr">
+      <c r="E751" t="inlineStr">
         <is>
           <t>Recepcion Conforme</t>
         </is>
       </c>
-      <c r="F750" t="inlineStr">
+      <c r="F751" t="inlineStr">
         <is>
           <t>70.882.100-4</t>
         </is>
       </c>
-      <c r="G750" t="inlineStr">
+      <c r="G751" t="inlineStr">
         <is>
           <t>CORPORACION MUNICIPAL DE MARÍA PINTO</t>
         </is>
       </c>
-      <c r="H750" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I750" t="inlineStr">
-        <is>
-          <t>COPEC S.A.</t>
-        </is>
-      </c>
-      <c r="J750" t="inlineStr">
-        <is>
-          <t>99.520.000-7</t>
-        </is>
-      </c>
-      <c r="K750" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L750" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M750" s="2" t="n">
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L751" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M751" s="2" t="n">
         <v>3994.06</v>
       </c>
     </row>
